--- a/research/traditional_assets/database/data/jordan/jordan_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0944510349951883</v>
+        <v>0.09429813292519793</v>
       </c>
       <c r="C2">
-        <v>1119.0072455111</v>
+        <v>1110.646368653884</v>
       </c>
       <c r="D2">
-        <v>1045.2072455111</v>
+        <v>1047.460368653884</v>
       </c>
       <c r="E2">
-        <v>-305.5</v>
+        <v>-294.886</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.614</v>
       </c>
       <c r="G2">
         <v>73.8</v>
@@ -1451,28 +1451,28 @@
         <v>107.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5338842</v>
       </c>
       <c r="N2">
-        <v>107.1</v>
+        <v>106.5661158</v>
       </c>
       <c r="O2">
-        <v>21.42</v>
+        <v>21.31322316</v>
       </c>
       <c r="P2">
-        <v>85.67999999999999</v>
+        <v>85.25289264</v>
       </c>
       <c r="Q2">
-        <v>199.58</v>
+        <v>199.15289264</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0944510349951883</v>
+        <v>0.09484417467191709</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5370538146839923</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>200.6052998009681</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09429813292519793</v>
+        <v>0.09414523085520753</v>
       </c>
       <c r="C3">
-        <v>1110.646368653884</v>
+        <v>1102.29522676734</v>
       </c>
       <c r="D3">
-        <v>1047.460368653884</v>
+        <v>1049.72322676734</v>
       </c>
       <c r="E3">
-        <v>-294.886</v>
+        <v>-284.272</v>
       </c>
       <c r="F3">
-        <v>10.614</v>
+        <v>21.228</v>
       </c>
       <c r="G3">
         <v>73.8</v>
@@ -1533,28 +1533,28 @@
         <v>107.1</v>
       </c>
       <c r="M3">
-        <v>0.5338842</v>
+        <v>1.0677684</v>
       </c>
       <c r="N3">
-        <v>106.5661158</v>
+        <v>106.0322316</v>
       </c>
       <c r="O3">
-        <v>21.31322316</v>
+        <v>21.20644632</v>
       </c>
       <c r="P3">
-        <v>85.25289264</v>
+        <v>84.82578527999999</v>
       </c>
       <c r="Q3">
-        <v>199.15289264</v>
+        <v>198.72578528</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09484417467191709</v>
+        <v>0.09524533760735462</v>
       </c>
       <c r="T3">
-        <v>0.5370538146839923</v>
+        <v>0.5414467132540629</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>200.6052998009681</v>
+        <v>100.302649900484</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09414523085520753</v>
+        <v>0.09399232878521716</v>
       </c>
       <c r="C4">
-        <v>1102.29522676734</v>
+        <v>1093.953883080255</v>
       </c>
       <c r="D4">
-        <v>1049.72322676734</v>
+        <v>1051.995883080255</v>
       </c>
       <c r="E4">
-        <v>-284.272</v>
+        <v>-273.658</v>
       </c>
       <c r="F4">
-        <v>21.228</v>
+        <v>31.842</v>
       </c>
       <c r="G4">
         <v>73.8</v>
@@ -1615,28 +1615,28 @@
         <v>107.1</v>
       </c>
       <c r="M4">
-        <v>1.0677684</v>
+        <v>1.6016526</v>
       </c>
       <c r="N4">
-        <v>106.0322316</v>
+        <v>105.4983474</v>
       </c>
       <c r="O4">
-        <v>21.20644632</v>
+        <v>21.09966948</v>
       </c>
       <c r="P4">
-        <v>84.82578527999999</v>
+        <v>84.39867792</v>
       </c>
       <c r="Q4">
-        <v>198.72578528</v>
+        <v>198.29867792</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09524533760735462</v>
+        <v>0.09565477194352284</v>
       </c>
       <c r="T4">
-        <v>0.5414467132540629</v>
+        <v>0.5459301870523824</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.302649900484</v>
+        <v>66.86843326698936</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09399232878521716</v>
+        <v>0.09383942671522678</v>
       </c>
       <c r="C5">
-        <v>1093.953883080255</v>
+        <v>1085.622401370169</v>
       </c>
       <c r="D5">
-        <v>1051.995883080255</v>
+        <v>1054.278401370169</v>
       </c>
       <c r="E5">
-        <v>-273.658</v>
+        <v>-263.044</v>
       </c>
       <c r="F5">
-        <v>31.842</v>
+        <v>42.456</v>
       </c>
       <c r="G5">
         <v>73.8</v>
@@ -1697,28 +1697,28 @@
         <v>107.1</v>
       </c>
       <c r="M5">
-        <v>1.6016526</v>
+        <v>2.1355368</v>
       </c>
       <c r="N5">
-        <v>105.4983474</v>
+        <v>104.9644632</v>
       </c>
       <c r="O5">
-        <v>21.09966948</v>
+        <v>20.99289264</v>
       </c>
       <c r="P5">
-        <v>84.39867792</v>
+        <v>83.97157056</v>
       </c>
       <c r="Q5">
-        <v>198.29867792</v>
+        <v>197.87157056</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09565477194352284</v>
+        <v>0.09607273616169457</v>
       </c>
       <c r="T5">
-        <v>0.5459301870523824</v>
+        <v>0.5505070665548337</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.86843326698936</v>
+        <v>50.15132495024201</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09383942671522678</v>
+        <v>0.0936865246452364</v>
       </c>
       <c r="C6">
-        <v>1085.622401370169</v>
+        <v>1077.300845969338</v>
       </c>
       <c r="D6">
-        <v>1054.278401370169</v>
+        <v>1056.570845969338</v>
       </c>
       <c r="E6">
-        <v>-263.044</v>
+        <v>-252.43</v>
       </c>
       <c r="F6">
-        <v>42.456</v>
+        <v>53.07000000000001</v>
       </c>
       <c r="G6">
         <v>73.8</v>
@@ -1779,28 +1779,28 @@
         <v>107.1</v>
       </c>
       <c r="M6">
-        <v>2.1355368</v>
+        <v>2.669421</v>
       </c>
       <c r="N6">
-        <v>104.9644632</v>
+        <v>104.430579</v>
       </c>
       <c r="O6">
-        <v>20.99289264</v>
+        <v>20.8861158</v>
       </c>
       <c r="P6">
-        <v>83.97157056</v>
+        <v>83.5444632</v>
       </c>
       <c r="Q6">
-        <v>197.87157056</v>
+        <v>197.4444632</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09607273616169457</v>
+        <v>0.09649949962656464</v>
       </c>
       <c r="T6">
-        <v>0.5505070665548337</v>
+        <v>0.5551803014152312</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.15132495024201</v>
+        <v>40.12105996019361</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0936865246452364</v>
+        <v>0.09353362257524603</v>
       </c>
       <c r="C7">
-        <v>1077.300845969338</v>
+        <v>1068.989281770778</v>
       </c>
       <c r="D7">
-        <v>1056.570845969338</v>
+        <v>1058.873281770778</v>
       </c>
       <c r="E7">
-        <v>-252.43</v>
+        <v>-241.816</v>
       </c>
       <c r="F7">
-        <v>53.07000000000001</v>
+        <v>63.68400000000001</v>
       </c>
       <c r="G7">
         <v>73.8</v>
@@ -1861,28 +1861,28 @@
         <v>107.1</v>
       </c>
       <c r="M7">
-        <v>2.669421</v>
+        <v>3.2033052</v>
       </c>
       <c r="N7">
-        <v>104.430579</v>
+        <v>103.8966948</v>
       </c>
       <c r="O7">
-        <v>20.8861158</v>
+        <v>20.77933896</v>
       </c>
       <c r="P7">
-        <v>83.5444632</v>
+        <v>83.11735583999999</v>
       </c>
       <c r="Q7">
-        <v>197.4444632</v>
+        <v>197.01735584</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09649949962656464</v>
+        <v>0.09693534316515535</v>
       </c>
       <c r="T7">
-        <v>0.5551803014152312</v>
+        <v>0.5599529668045735</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.12105996019361</v>
+        <v>33.43421663349467</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09353362257524603</v>
+        <v>0.09338072050525566</v>
       </c>
       <c r="C8">
-        <v>1068.989281770778</v>
+        <v>1060.68777423439</v>
       </c>
       <c r="D8">
-        <v>1058.873281770778</v>
+        <v>1061.18577423439</v>
       </c>
       <c r="E8">
-        <v>-241.816</v>
+        <v>-231.202</v>
       </c>
       <c r="F8">
-        <v>63.684</v>
+        <v>74.298</v>
       </c>
       <c r="G8">
         <v>73.8</v>
@@ -1943,28 +1943,28 @@
         <v>107.1</v>
       </c>
       <c r="M8">
-        <v>3.2033052</v>
+        <v>3.7371894</v>
       </c>
       <c r="N8">
-        <v>103.8966948</v>
+        <v>103.3628106</v>
       </c>
       <c r="O8">
-        <v>20.77933896</v>
+        <v>20.67256212</v>
       </c>
       <c r="P8">
-        <v>83.11735583999999</v>
+        <v>82.69024847999999</v>
       </c>
       <c r="Q8">
-        <v>197.01735584</v>
+        <v>196.59024848</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09693534316515535</v>
+        <v>0.09738055968307061</v>
       </c>
       <c r="T8">
-        <v>0.5599529668045735</v>
+        <v>0.5648282701592779</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.43421663349468</v>
+        <v>28.65789997156686</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09338072050525566</v>
+        <v>0.0932278184352653</v>
       </c>
       <c r="C9">
-        <v>1060.68777423439</v>
+        <v>1052.396389393162</v>
       </c>
       <c r="D9">
-        <v>1061.18577423439</v>
+        <v>1063.508389393162</v>
       </c>
       <c r="E9">
-        <v>-231.202</v>
+        <v>-220.588</v>
       </c>
       <c r="F9">
-        <v>74.29800000000002</v>
+        <v>84.91200000000001</v>
       </c>
       <c r="G9">
         <v>73.8</v>
@@ -2025,28 +2025,28 @@
         <v>107.1</v>
       </c>
       <c r="M9">
-        <v>3.737189400000001</v>
+        <v>4.2710736</v>
       </c>
       <c r="N9">
-        <v>103.3628106</v>
+        <v>102.8289264</v>
       </c>
       <c r="O9">
-        <v>20.67256212</v>
+        <v>20.56578528</v>
       </c>
       <c r="P9">
-        <v>82.69024847999999</v>
+        <v>82.26314112</v>
       </c>
       <c r="Q9">
-        <v>196.59024848</v>
+        <v>196.16314112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09738055968307061</v>
+        <v>0.09783545482094053</v>
       </c>
       <c r="T9">
-        <v>0.5648282701592779</v>
+        <v>0.5698095583695193</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.65789997156686</v>
+        <v>25.07566247512101</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0932278184352653</v>
+        <v>0.09307491636527492</v>
       </c>
       <c r="C10">
-        <v>1052.396389393162</v>
+        <v>1044.115193859456</v>
       </c>
       <c r="D10">
-        <v>1063.508389393162</v>
+        <v>1065.841193859456</v>
       </c>
       <c r="E10">
-        <v>-220.588</v>
+        <v>-209.974</v>
       </c>
       <c r="F10">
-        <v>84.91200000000001</v>
+        <v>95.52600000000001</v>
       </c>
       <c r="G10">
         <v>73.8</v>
@@ -2107,28 +2107,28 @@
         <v>107.1</v>
       </c>
       <c r="M10">
-        <v>4.2710736</v>
+        <v>4.8049578</v>
       </c>
       <c r="N10">
-        <v>102.8289264</v>
+        <v>102.2950422</v>
       </c>
       <c r="O10">
-        <v>20.56578528</v>
+        <v>20.45900844</v>
       </c>
       <c r="P10">
-        <v>82.26314112</v>
+        <v>81.83603375999999</v>
       </c>
       <c r="Q10">
-        <v>196.16314112</v>
+        <v>195.73603376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09783545482094053</v>
+        <v>0.09830034765414825</v>
       </c>
       <c r="T10">
-        <v>0.5698095583695193</v>
+        <v>0.5749003254415243</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.07566247512101</v>
+        <v>22.28947775566312</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09307491636527492</v>
+        <v>0.09292201429528452</v>
       </c>
       <c r="C11">
-        <v>1044.115193859456</v>
+        <v>1035.844254831375</v>
       </c>
       <c r="D11">
-        <v>1065.841193859456</v>
+        <v>1068.184254831375</v>
       </c>
       <c r="E11">
-        <v>-209.974</v>
+        <v>-199.36</v>
       </c>
       <c r="F11">
-        <v>95.52600000000001</v>
+        <v>106.14</v>
       </c>
       <c r="G11">
         <v>73.8</v>
@@ -2189,28 +2189,28 @@
         <v>107.1</v>
       </c>
       <c r="M11">
-        <v>4.8049578</v>
+        <v>5.338842</v>
       </c>
       <c r="N11">
-        <v>102.2950422</v>
+        <v>101.761158</v>
       </c>
       <c r="O11">
-        <v>20.45900844</v>
+        <v>20.3522316</v>
       </c>
       <c r="P11">
-        <v>81.83603375999999</v>
+        <v>81.4089264</v>
       </c>
       <c r="Q11">
-        <v>195.73603376</v>
+        <v>195.3089264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09830034765414825</v>
+        <v>0.09877557143920501</v>
       </c>
       <c r="T11">
-        <v>0.5749003254415243</v>
+        <v>0.5801042206706849</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.28947775566312</v>
+        <v>20.06052998009681</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09292201429528454</v>
+        <v>0.09276911222529415</v>
       </c>
       <c r="C12">
-        <v>1035.844254831375</v>
+        <v>1027.583640099217</v>
       </c>
       <c r="D12">
-        <v>1068.184254831375</v>
+        <v>1070.537640099217</v>
       </c>
       <c r="E12">
-        <v>-199.36</v>
+        <v>-188.746</v>
       </c>
       <c r="F12">
-        <v>106.14</v>
+        <v>116.754</v>
       </c>
       <c r="G12">
         <v>73.8</v>
@@ -2271,28 +2271,28 @@
         <v>107.1</v>
       </c>
       <c r="M12">
-        <v>5.338842000000001</v>
+        <v>5.8727262</v>
       </c>
       <c r="N12">
-        <v>101.761158</v>
+        <v>101.2272738</v>
       </c>
       <c r="O12">
-        <v>20.3522316</v>
+        <v>20.24545476</v>
       </c>
       <c r="P12">
-        <v>81.4089264</v>
+        <v>80.98181903999999</v>
       </c>
       <c r="Q12">
-        <v>195.3089264</v>
+        <v>194.88181904</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09877557143920504</v>
+        <v>0.09926147441044286</v>
       </c>
       <c r="T12">
-        <v>0.580104220670685</v>
+        <v>0.5854250573656694</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.06052998009681</v>
+        <v>18.23684543645164</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09276911222529415</v>
+        <v>0.09261621015530377</v>
       </c>
       <c r="C13">
-        <v>1027.583640099217</v>
+        <v>1019.333418052008</v>
       </c>
       <c r="D13">
-        <v>1070.537640099217</v>
+        <v>1072.901418052008</v>
       </c>
       <c r="E13">
-        <v>-188.746</v>
+        <v>-178.132</v>
       </c>
       <c r="F13">
-        <v>116.754</v>
+        <v>127.368</v>
       </c>
       <c r="G13">
         <v>73.8</v>
@@ -2353,28 +2353,28 @@
         <v>107.1</v>
       </c>
       <c r="M13">
-        <v>5.8727262</v>
+        <v>6.4066104</v>
       </c>
       <c r="N13">
-        <v>101.2272738</v>
+        <v>100.6933896</v>
       </c>
       <c r="O13">
-        <v>20.24545476</v>
+        <v>20.13867792</v>
       </c>
       <c r="P13">
-        <v>80.98181903999999</v>
+        <v>80.55471168</v>
       </c>
       <c r="Q13">
-        <v>194.88181904</v>
+        <v>194.45471168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09926147441044286</v>
+        <v>0.09975842063102702</v>
       </c>
       <c r="T13">
-        <v>0.5854250573656694</v>
+        <v>0.5908668221673582</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.23684543645164</v>
+        <v>16.71710831674734</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09261621015530377</v>
+        <v>0.0924633080853134</v>
       </c>
       <c r="C14">
-        <v>1019.333418052008</v>
+        <v>1011.093657684135</v>
       </c>
       <c r="D14">
-        <v>1072.901418052008</v>
+        <v>1075.275657684135</v>
       </c>
       <c r="E14">
-        <v>-178.132</v>
+        <v>-167.518</v>
       </c>
       <c r="F14">
-        <v>127.368</v>
+        <v>137.982</v>
       </c>
       <c r="G14">
         <v>73.8</v>
@@ -2435,28 +2435,28 @@
         <v>107.1</v>
       </c>
       <c r="M14">
-        <v>6.4066104</v>
+        <v>6.940494600000001</v>
       </c>
       <c r="N14">
-        <v>100.6933896</v>
+        <v>100.1595054</v>
       </c>
       <c r="O14">
-        <v>20.13867792</v>
+        <v>20.03190108</v>
       </c>
       <c r="P14">
-        <v>80.55471168</v>
+        <v>80.12760432</v>
       </c>
       <c r="Q14">
-        <v>194.45471168</v>
+        <v>194.02760432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09975842063102702</v>
+        <v>0.1002667909026591</v>
       </c>
       <c r="T14">
-        <v>0.5908668221673582</v>
+        <v>0.596433685010465</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.71710831674734</v>
+        <v>15.43117690776677</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0924633080853134</v>
+        <v>0.09231040601532302</v>
       </c>
       <c r="C15">
-        <v>1011.093657684135</v>
+        <v>1002.864428602051</v>
       </c>
       <c r="D15">
-        <v>1075.275657684135</v>
+        <v>1077.660428602051</v>
       </c>
       <c r="E15">
-        <v>-167.518</v>
+        <v>-156.904</v>
       </c>
       <c r="F15">
-        <v>137.982</v>
+        <v>148.596</v>
       </c>
       <c r="G15">
         <v>73.8</v>
@@ -2517,28 +2517,28 @@
         <v>107.1</v>
       </c>
       <c r="M15">
-        <v>6.940494600000001</v>
+        <v>7.474378800000001</v>
       </c>
       <c r="N15">
-        <v>100.1595054</v>
+        <v>99.6256212</v>
       </c>
       <c r="O15">
-        <v>20.03190108</v>
+        <v>19.92512424</v>
       </c>
       <c r="P15">
-        <v>80.12760432</v>
+        <v>79.70049696</v>
       </c>
       <c r="Q15">
-        <v>194.02760432</v>
+        <v>193.60049696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1002667909026591</v>
+        <v>0.1007869837387477</v>
       </c>
       <c r="T15">
-        <v>0.596433685010465</v>
+        <v>0.6021300097801557</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.43117690776677</v>
+        <v>14.32894998578343</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09231040601532302</v>
+        <v>0.09215750394533265</v>
       </c>
       <c r="C16">
-        <v>1002.864428602051</v>
+        <v>994.645801031083</v>
       </c>
       <c r="D16">
-        <v>1077.660428602051</v>
+        <v>1080.055801031083</v>
       </c>
       <c r="E16">
-        <v>-156.904</v>
+        <v>-146.29</v>
       </c>
       <c r="F16">
-        <v>148.596</v>
+        <v>159.21</v>
       </c>
       <c r="G16">
         <v>73.8</v>
@@ -2599,28 +2599,28 @@
         <v>107.1</v>
       </c>
       <c r="M16">
-        <v>7.474378800000001</v>
+        <v>8.008263000000001</v>
       </c>
       <c r="N16">
-        <v>99.6256212</v>
+        <v>99.09173699999999</v>
       </c>
       <c r="O16">
-        <v>19.92512424</v>
+        <v>19.8183474</v>
       </c>
       <c r="P16">
-        <v>79.70049696</v>
+        <v>79.2733896</v>
       </c>
       <c r="Q16">
-        <v>193.60049696</v>
+        <v>193.1733896</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1007869837387477</v>
+        <v>0.1013194164062737</v>
       </c>
       <c r="T16">
-        <v>0.6021300097801557</v>
+        <v>0.607960365720898</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.32894998578343</v>
+        <v>13.37368665339787</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09215750394533265</v>
+        <v>0.09219660187534225</v>
       </c>
       <c r="C17">
-        <v>994.645801031083</v>
+        <v>983.4182779098005</v>
       </c>
       <c r="D17">
-        <v>1080.055801031083</v>
+        <v>1079.442277909801</v>
       </c>
       <c r="E17">
-        <v>-146.29</v>
+        <v>-135.676</v>
       </c>
       <c r="F17">
-        <v>159.21</v>
+        <v>169.824</v>
       </c>
       <c r="G17">
         <v>73.8</v>
@@ -2681,45 +2681,45 @@
         <v>107.1</v>
       </c>
       <c r="M17">
-        <v>8.008262999999999</v>
+        <v>8.7968832</v>
       </c>
       <c r="N17">
-        <v>99.09173699999999</v>
+        <v>98.3031168</v>
       </c>
       <c r="O17">
-        <v>19.8183474</v>
+        <v>19.66062336</v>
       </c>
       <c r="P17">
-        <v>79.2733896</v>
+        <v>78.64249344</v>
       </c>
       <c r="Q17">
-        <v>193.1733896</v>
+        <v>192.54249344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1013194164062737</v>
+        <v>0.1018645260420741</v>
       </c>
       <c r="T17">
-        <v>0.607960365720898</v>
+        <v>0.6139295396602292</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.37368665339787</v>
+        <v>12.17476662643424</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09219660187534225</v>
+        <v>0.09205569980535189</v>
       </c>
       <c r="C18">
-        <v>983.4182779098005</v>
+        <v>975.0185844727288</v>
       </c>
       <c r="D18">
-        <v>1079.442277909801</v>
+        <v>1081.656584472729</v>
       </c>
       <c r="E18">
-        <v>-135.676</v>
+        <v>-125.062</v>
       </c>
       <c r="F18">
-        <v>169.824</v>
+        <v>180.438</v>
       </c>
       <c r="G18">
         <v>73.8</v>
@@ -2763,28 +2763,28 @@
         <v>107.1</v>
       </c>
       <c r="M18">
-        <v>8.7968832</v>
+        <v>9.346688400000001</v>
       </c>
       <c r="N18">
-        <v>98.3031168</v>
+        <v>97.75331159999999</v>
       </c>
       <c r="O18">
-        <v>19.66062336</v>
+        <v>19.55066232</v>
       </c>
       <c r="P18">
-        <v>78.64249344</v>
+        <v>78.20264927999999</v>
       </c>
       <c r="Q18">
-        <v>192.54249344</v>
+        <v>192.10264928</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1018645260420741</v>
+        <v>0.1024227708498216</v>
       </c>
       <c r="T18">
-        <v>0.6139295396602292</v>
+        <v>0.6200425491161711</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.17476662643424</v>
+        <v>11.45860388370281</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09205569980535189</v>
+        <v>0.09191479773536151</v>
       </c>
       <c r="C19">
-        <v>975.0185844727288</v>
+        <v>966.6279943149724</v>
       </c>
       <c r="D19">
-        <v>1081.656584472729</v>
+        <v>1083.879994314972</v>
       </c>
       <c r="E19">
-        <v>-125.062</v>
+        <v>-114.448</v>
       </c>
       <c r="F19">
-        <v>180.438</v>
+        <v>191.052</v>
       </c>
       <c r="G19">
         <v>73.8</v>
@@ -2845,28 +2845,28 @@
         <v>107.1</v>
       </c>
       <c r="M19">
-        <v>9.346688400000001</v>
+        <v>9.896493600000003</v>
       </c>
       <c r="N19">
-        <v>97.75331159999999</v>
+        <v>97.20350639999999</v>
       </c>
       <c r="O19">
-        <v>19.55066232</v>
+        <v>19.44070128</v>
       </c>
       <c r="P19">
-        <v>78.20264927999999</v>
+        <v>77.76280512</v>
       </c>
       <c r="Q19">
-        <v>192.10264928</v>
+        <v>191.66280512</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1024227708498216</v>
+        <v>0.1029946313845872</v>
       </c>
       <c r="T19">
-        <v>0.6200425491161711</v>
+        <v>0.6263046563637212</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.45860388370281</v>
+        <v>10.82201477905265</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09191479773536151</v>
+        <v>0.09177389566537114</v>
       </c>
       <c r="C20">
-        <v>966.6279943149724</v>
+        <v>958.2465636891681</v>
       </c>
       <c r="D20">
-        <v>1083.879994314972</v>
+        <v>1086.112563689168</v>
       </c>
       <c r="E20">
-        <v>-114.448</v>
+        <v>-103.834</v>
       </c>
       <c r="F20">
-        <v>191.052</v>
+        <v>201.666</v>
       </c>
       <c r="G20">
         <v>73.8</v>
@@ -2927,28 +2927,28 @@
         <v>107.1</v>
       </c>
       <c r="M20">
-        <v>9.896493600000001</v>
+        <v>10.4462988</v>
       </c>
       <c r="N20">
-        <v>97.20350639999999</v>
+        <v>96.6537012</v>
       </c>
       <c r="O20">
-        <v>19.44070128</v>
+        <v>19.33074024</v>
       </c>
       <c r="P20">
-        <v>77.76280512</v>
+        <v>77.32296096</v>
       </c>
       <c r="Q20">
-        <v>191.66280512</v>
+        <v>191.22296096</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1029946313845872</v>
+        <v>0.103580611932557</v>
       </c>
       <c r="T20">
-        <v>0.6263046563637211</v>
+        <v>0.6327213835433095</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.82201477905265</v>
+        <v>10.25243505383935</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09177389566537114</v>
+        <v>0.09190499359538076</v>
       </c>
       <c r="C21">
-        <v>958.2465636891681</v>
+        <v>945.5550421036792</v>
       </c>
       <c r="D21">
-        <v>1086.112563689168</v>
+        <v>1084.035042103679</v>
       </c>
       <c r="E21">
-        <v>-103.834</v>
+        <v>-93.21999999999997</v>
       </c>
       <c r="F21">
-        <v>201.666</v>
+        <v>212.28</v>
       </c>
       <c r="G21">
         <v>73.8</v>
@@ -3009,45 +3009,45 @@
         <v>107.1</v>
       </c>
       <c r="M21">
-        <v>10.4462988</v>
+        <v>11.35698</v>
       </c>
       <c r="N21">
-        <v>96.6537012</v>
+        <v>95.74301999999999</v>
       </c>
       <c r="O21">
-        <v>19.33074024</v>
+        <v>19.148604</v>
       </c>
       <c r="P21">
-        <v>77.32296096</v>
+        <v>76.594416</v>
       </c>
       <c r="Q21">
-        <v>191.22296096</v>
+        <v>190.494416</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.103580611932557</v>
+        <v>0.1041812419942259</v>
       </c>
       <c r="T21">
-        <v>0.6327213835433095</v>
+        <v>0.6392985289023875</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.25243505383935</v>
+        <v>9.430323906531488</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09190499359538076</v>
+        <v>0.09177769152539038</v>
       </c>
       <c r="C22">
-        <v>945.5550421036792</v>
+        <v>936.9582983900229</v>
       </c>
       <c r="D22">
-        <v>1084.035042103679</v>
+        <v>1086.052298390023</v>
       </c>
       <c r="E22">
-        <v>-93.21999999999997</v>
+        <v>-82.60599999999997</v>
       </c>
       <c r="F22">
-        <v>212.28</v>
+        <v>222.894</v>
       </c>
       <c r="G22">
         <v>73.8</v>
@@ -3091,28 +3091,28 @@
         <v>107.1</v>
       </c>
       <c r="M22">
-        <v>11.35698</v>
+        <v>11.924829</v>
       </c>
       <c r="N22">
-        <v>95.74301999999999</v>
+        <v>95.17517099999999</v>
       </c>
       <c r="O22">
-        <v>19.148604</v>
+        <v>19.0350342</v>
       </c>
       <c r="P22">
-        <v>76.594416</v>
+        <v>76.14013679999999</v>
       </c>
       <c r="Q22">
-        <v>190.494416</v>
+        <v>190.0401368</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1041812419942259</v>
+        <v>0.104797077880241</v>
       </c>
       <c r="T22">
-        <v>0.6392985289023875</v>
+        <v>0.6460421842705562</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.430323906531488</v>
+        <v>8.981260863363323</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09177769152539038</v>
+        <v>0.09165038945540002</v>
       </c>
       <c r="C23">
-        <v>936.9582983900229</v>
+        <v>928.3690764065602</v>
       </c>
       <c r="D23">
-        <v>1086.052298390023</v>
+        <v>1088.07707640656</v>
       </c>
       <c r="E23">
-        <v>-82.60599999999999</v>
+        <v>-71.99199999999999</v>
       </c>
       <c r="F23">
-        <v>222.894</v>
+        <v>233.508</v>
       </c>
       <c r="G23">
         <v>73.8</v>
@@ -3173,28 +3173,28 @@
         <v>107.1</v>
       </c>
       <c r="M23">
-        <v>11.924829</v>
+        <v>12.492678</v>
       </c>
       <c r="N23">
-        <v>95.17517099999999</v>
+        <v>94.607322</v>
       </c>
       <c r="O23">
-        <v>19.0350342</v>
+        <v>18.9214644</v>
       </c>
       <c r="P23">
-        <v>76.14013679999999</v>
+        <v>75.68585759999999</v>
       </c>
       <c r="Q23">
-        <v>190.0401368</v>
+        <v>189.5858576</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.104797077880241</v>
+        <v>0.10542870443</v>
       </c>
       <c r="T23">
-        <v>0.6460421842705562</v>
+        <v>0.6529587538789343</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.981260863363323</v>
+        <v>8.573021733210446</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09165038945540002</v>
+        <v>0.09152308738540964</v>
       </c>
       <c r="C24">
-        <v>928.3690764065602</v>
+        <v>919.7874183012084</v>
       </c>
       <c r="D24">
-        <v>1088.07707640656</v>
+        <v>1090.109418301209</v>
       </c>
       <c r="E24">
-        <v>-71.99199999999999</v>
+        <v>-61.37799999999996</v>
       </c>
       <c r="F24">
-        <v>233.508</v>
+        <v>244.122</v>
       </c>
       <c r="G24">
         <v>73.8</v>
@@ -3255,28 +3255,28 @@
         <v>107.1</v>
       </c>
       <c r="M24">
-        <v>12.492678</v>
+        <v>13.060527</v>
       </c>
       <c r="N24">
-        <v>94.607322</v>
+        <v>94.03947299999999</v>
       </c>
       <c r="O24">
-        <v>18.9214644</v>
+        <v>18.8078946</v>
       </c>
       <c r="P24">
-        <v>75.68585759999999</v>
+        <v>75.23157839999999</v>
       </c>
       <c r="Q24">
-        <v>189.5858576</v>
+        <v>189.1315784</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.10542870443</v>
+        <v>0.1060767368641684</v>
       </c>
       <c r="T24">
-        <v>0.6529587538789343</v>
+        <v>0.6600549746459716</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.573021733210446</v>
+        <v>8.200281657853466</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09152308738540964</v>
+        <v>0.09139578531541927</v>
       </c>
       <c r="C25">
-        <v>919.7874183012084</v>
+        <v>911.2133665373735</v>
       </c>
       <c r="D25">
-        <v>1090.109418301209</v>
+        <v>1092.149366537374</v>
       </c>
       <c r="E25">
-        <v>-61.37799999999996</v>
+        <v>-50.76399999999995</v>
       </c>
       <c r="F25">
-        <v>244.122</v>
+        <v>254.736</v>
       </c>
       <c r="G25">
         <v>73.8</v>
@@ -3337,28 +3337,28 @@
         <v>107.1</v>
       </c>
       <c r="M25">
-        <v>13.060527</v>
+        <v>13.628376</v>
       </c>
       <c r="N25">
-        <v>94.03947299999999</v>
+        <v>93.47162399999999</v>
       </c>
       <c r="O25">
-        <v>18.8078946</v>
+        <v>18.6943248</v>
       </c>
       <c r="P25">
-        <v>75.23157839999999</v>
+        <v>74.77729919999999</v>
       </c>
       <c r="Q25">
-        <v>189.1315784</v>
+        <v>188.6772992</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1060767368641684</v>
+        <v>0.1067418227834464</v>
       </c>
       <c r="T25">
-        <v>0.6600549746459716</v>
+        <v>0.667337938064773</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.200281657853466</v>
+        <v>7.858603255442906</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09139578531541925</v>
+        <v>0.09142848324542888</v>
       </c>
       <c r="C26">
-        <v>911.2133665373736</v>
+        <v>900.0746712154324</v>
       </c>
       <c r="D26">
-        <v>1092.149366537374</v>
+        <v>1091.624671215432</v>
       </c>
       <c r="E26">
-        <v>-50.76399999999998</v>
+        <v>-40.14999999999998</v>
       </c>
       <c r="F26">
-        <v>254.736</v>
+        <v>265.35</v>
       </c>
       <c r="G26">
         <v>73.8</v>
@@ -3419,45 +3419,45 @@
         <v>107.1</v>
       </c>
       <c r="M26">
-        <v>13.628376</v>
+        <v>14.408505</v>
       </c>
       <c r="N26">
-        <v>93.47162399999999</v>
+        <v>92.69149499999999</v>
       </c>
       <c r="O26">
-        <v>18.6943248</v>
+        <v>18.538299</v>
       </c>
       <c r="P26">
-        <v>74.77729919999999</v>
+        <v>74.15319599999999</v>
       </c>
       <c r="Q26">
-        <v>188.6772992</v>
+        <v>188.053196</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1067418227834464</v>
+        <v>0.1074246443272385</v>
       </c>
       <c r="T26">
-        <v>0.6673379380647729</v>
+        <v>0.674815113841409</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.858603255442907</v>
+        <v>7.433109819512849</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09142848324542888</v>
+        <v>0.09130758117543848</v>
       </c>
       <c r="C27">
-        <v>900.0746712154324</v>
+        <v>891.4032745771441</v>
       </c>
       <c r="D27">
-        <v>1091.624671215432</v>
+        <v>1093.567274577144</v>
       </c>
       <c r="E27">
-        <v>-40.14999999999998</v>
+        <v>-29.53599999999994</v>
       </c>
       <c r="F27">
-        <v>265.35</v>
+        <v>275.9640000000001</v>
       </c>
       <c r="G27">
         <v>73.8</v>
@@ -3501,28 +3501,28 @@
         <v>107.1</v>
       </c>
       <c r="M27">
-        <v>14.408505</v>
+        <v>14.9848452</v>
       </c>
       <c r="N27">
-        <v>92.69149499999999</v>
+        <v>92.11515479999998</v>
       </c>
       <c r="O27">
-        <v>18.538299</v>
+        <v>18.42303096</v>
       </c>
       <c r="P27">
-        <v>74.15319599999999</v>
+        <v>73.69212383999999</v>
       </c>
       <c r="Q27">
-        <v>188.053196</v>
+        <v>187.59212384</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1074246443272385</v>
+        <v>0.1081259205073493</v>
       </c>
       <c r="T27">
-        <v>0.674815113841409</v>
+        <v>0.6824943754498461</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.433109819512849</v>
+        <v>7.147220980300815</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09130758117543848</v>
+        <v>0.09118667910544812</v>
       </c>
       <c r="C28">
-        <v>891.4032745771441</v>
+        <v>882.7388041936451</v>
       </c>
       <c r="D28">
-        <v>1093.567274577144</v>
+        <v>1095.516804193645</v>
       </c>
       <c r="E28">
-        <v>-29.53599999999994</v>
+        <v>-18.92199999999997</v>
       </c>
       <c r="F28">
-        <v>275.9640000000001</v>
+        <v>286.578</v>
       </c>
       <c r="G28">
         <v>73.8</v>
@@ -3583,28 +3583,28 @@
         <v>107.1</v>
       </c>
       <c r="M28">
-        <v>14.9848452</v>
+        <v>15.5611854</v>
       </c>
       <c r="N28">
-        <v>92.11515479999998</v>
+        <v>91.53881459999999</v>
       </c>
       <c r="O28">
-        <v>18.42303096</v>
+        <v>18.30776292</v>
       </c>
       <c r="P28">
-        <v>73.69212383999999</v>
+        <v>73.23105167999999</v>
       </c>
       <c r="Q28">
-        <v>187.59212384</v>
+        <v>187.13105168</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1081259205073493</v>
+        <v>0.1088464097334906</v>
       </c>
       <c r="T28">
-        <v>0.6824943754498461</v>
+        <v>0.6903840277872816</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.147220980300815</v>
+        <v>6.882509092141527</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09118667910544812</v>
+        <v>0.09106577703545775</v>
       </c>
       <c r="C29">
-        <v>882.7388041936451</v>
+        <v>874.0812971739117</v>
       </c>
       <c r="D29">
-        <v>1095.516804193645</v>
+        <v>1097.473297173912</v>
       </c>
       <c r="E29">
-        <v>-18.92199999999997</v>
+        <v>-8.307999999999936</v>
       </c>
       <c r="F29">
-        <v>286.578</v>
+        <v>297.1920000000001</v>
       </c>
       <c r="G29">
         <v>73.8</v>
@@ -3665,28 +3665,28 @@
         <v>107.1</v>
       </c>
       <c r="M29">
-        <v>15.5611854</v>
+        <v>16.1375256</v>
       </c>
       <c r="N29">
-        <v>91.53881459999999</v>
+        <v>90.96247439999999</v>
       </c>
       <c r="O29">
-        <v>18.30776292</v>
+        <v>18.19249488</v>
       </c>
       <c r="P29">
-        <v>73.23105167999999</v>
+        <v>72.76997951999999</v>
       </c>
       <c r="Q29">
-        <v>187.13105168</v>
+        <v>186.66997952</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1088464097334906</v>
+        <v>0.1095869125492469</v>
       </c>
       <c r="T29">
-        <v>0.6903840277872816</v>
+        <v>0.69849283713409</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.882509092141527</v>
+        <v>6.636705195993614</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09106577703545775</v>
+        <v>0.09094487496546737</v>
       </c>
       <c r="C30">
-        <v>874.0812971739117</v>
+        <v>865.4307908924875</v>
       </c>
       <c r="D30">
-        <v>1097.473297173912</v>
+        <v>1099.436790892488</v>
       </c>
       <c r="E30">
-        <v>-8.307999999999936</v>
+        <v>2.30600000000004</v>
       </c>
       <c r="F30">
-        <v>297.1920000000001</v>
+        <v>307.806</v>
       </c>
       <c r="G30">
         <v>73.8</v>
@@ -3747,28 +3747,28 @@
         <v>107.1</v>
       </c>
       <c r="M30">
-        <v>16.1375256</v>
+        <v>16.7138658</v>
       </c>
       <c r="N30">
-        <v>90.96247439999999</v>
+        <v>90.38613419999999</v>
       </c>
       <c r="O30">
-        <v>18.19249488</v>
+        <v>18.07722684</v>
       </c>
       <c r="P30">
-        <v>72.76997951999999</v>
+        <v>72.30890735999999</v>
       </c>
       <c r="Q30">
-        <v>186.66997952</v>
+        <v>186.20890736</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1095869125492469</v>
+        <v>0.1103482745992498</v>
       </c>
       <c r="T30">
-        <v>0.69849283713409</v>
+        <v>0.7068300636455975</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.636705195993614</v>
+        <v>6.407853292683489</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09094487496546737</v>
+        <v>0.090823972895477</v>
       </c>
       <c r="C31">
-        <v>865.4307908924875</v>
+        <v>856.7873229918619</v>
       </c>
       <c r="D31">
-        <v>1099.436790892488</v>
+        <v>1101.407322991862</v>
       </c>
       <c r="E31">
-        <v>2.305999999999983</v>
+        <v>12.92000000000002</v>
       </c>
       <c r="F31">
-        <v>307.806</v>
+        <v>318.42</v>
       </c>
       <c r="G31">
         <v>73.8</v>
@@ -3829,28 +3829,28 @@
         <v>107.1</v>
       </c>
       <c r="M31">
-        <v>16.7138658</v>
+        <v>17.290206</v>
       </c>
       <c r="N31">
-        <v>90.38613419999999</v>
+        <v>89.809794</v>
       </c>
       <c r="O31">
-        <v>18.07722684</v>
+        <v>17.9619588</v>
       </c>
       <c r="P31">
-        <v>72.30890735999999</v>
+        <v>71.84783519999999</v>
       </c>
       <c r="Q31">
-        <v>186.20890736</v>
+        <v>185.7478352</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1103482745992498</v>
+        <v>0.1111313898506814</v>
       </c>
       <c r="T31">
-        <v>0.7068300636455975</v>
+        <v>0.7154054966288623</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.40785329268349</v>
+        <v>6.194258182927374</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.090823972895477</v>
+        <v>0.09095107082548662</v>
       </c>
       <c r="C32">
-        <v>856.7873229918619</v>
+        <v>844.1019970820296</v>
       </c>
       <c r="D32">
-        <v>1101.407322991862</v>
+        <v>1099.33599708203</v>
       </c>
       <c r="E32">
-        <v>12.92000000000002</v>
+        <v>23.53400000000005</v>
       </c>
       <c r="F32">
-        <v>318.42</v>
+        <v>329.034</v>
       </c>
       <c r="G32">
         <v>73.8</v>
@@ -3911,45 +3911,45 @@
         <v>107.1</v>
       </c>
       <c r="M32">
-        <v>17.290206</v>
+        <v>18.1955802</v>
       </c>
       <c r="N32">
-        <v>89.809794</v>
+        <v>88.9044198</v>
       </c>
       <c r="O32">
-        <v>17.9619588</v>
+        <v>17.78088396</v>
       </c>
       <c r="P32">
-        <v>71.84783519999999</v>
+        <v>71.12353584</v>
       </c>
       <c r="Q32">
-        <v>185.7478352</v>
+        <v>185.02353584</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1111313898506814</v>
+        <v>0.1119372040949081</v>
       </c>
       <c r="T32">
-        <v>0.7154054966288623</v>
+        <v>0.7242294928870042</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.194258182927374</v>
+        <v>5.886044787953505</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09095107082548662</v>
+        <v>0.09083816875549622</v>
       </c>
       <c r="C33">
-        <v>844.1019970820296</v>
+        <v>835.3275847043745</v>
       </c>
       <c r="D33">
-        <v>1099.33599708203</v>
+        <v>1101.175584704375</v>
       </c>
       <c r="E33">
-        <v>23.53400000000005</v>
+        <v>34.14800000000002</v>
       </c>
       <c r="F33">
-        <v>329.034</v>
+        <v>339.648</v>
       </c>
       <c r="G33">
         <v>73.8</v>
@@ -3993,28 +3993,28 @@
         <v>107.1</v>
       </c>
       <c r="M33">
-        <v>18.1955802</v>
+        <v>18.7825344</v>
       </c>
       <c r="N33">
-        <v>88.9044198</v>
+        <v>88.31746559999999</v>
       </c>
       <c r="O33">
-        <v>17.78088396</v>
+        <v>17.66349312</v>
       </c>
       <c r="P33">
-        <v>71.12353584</v>
+        <v>70.65397247999999</v>
       </c>
       <c r="Q33">
-        <v>185.02353584</v>
+        <v>184.55397248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1119372040949081</v>
+        <v>0.1127667187580827</v>
       </c>
       <c r="T33">
-        <v>0.7242294928870042</v>
+        <v>0.7333130184468563</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.886044787953505</v>
+        <v>5.702105888329957</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09083816875549622</v>
+        <v>0.09072526668550587</v>
       </c>
       <c r="C34">
-        <v>835.3275847043745</v>
+        <v>826.5593392400514</v>
       </c>
       <c r="D34">
-        <v>1101.175584704375</v>
+        <v>1103.021339240051</v>
       </c>
       <c r="E34">
-        <v>34.14800000000002</v>
+        <v>44.76200000000006</v>
       </c>
       <c r="F34">
-        <v>339.648</v>
+        <v>350.2620000000001</v>
       </c>
       <c r="G34">
         <v>73.8</v>
@@ -4075,28 +4075,28 @@
         <v>107.1</v>
       </c>
       <c r="M34">
-        <v>18.7825344</v>
+        <v>19.3694886</v>
       </c>
       <c r="N34">
-        <v>88.31746559999999</v>
+        <v>87.73051139999998</v>
       </c>
       <c r="O34">
-        <v>17.66349312</v>
+        <v>17.54610228</v>
       </c>
       <c r="P34">
-        <v>70.65397247999999</v>
+        <v>70.18440911999998</v>
       </c>
       <c r="Q34">
-        <v>184.55397248</v>
+        <v>184.08440912</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1127667187580827</v>
+        <v>0.1136209950529938</v>
       </c>
       <c r="T34">
-        <v>0.7333130184468563</v>
+        <v>0.7426676940234204</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.702105888329957</v>
+        <v>5.529314800804806</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09072526668550587</v>
+        <v>0.09061236461551547</v>
       </c>
       <c r="C35">
-        <v>826.5593392400514</v>
+        <v>817.7972917514644</v>
       </c>
       <c r="D35">
-        <v>1103.021339240051</v>
+        <v>1104.873291751464</v>
       </c>
       <c r="E35">
-        <v>44.76200000000006</v>
+        <v>55.37600000000003</v>
       </c>
       <c r="F35">
-        <v>350.2620000000001</v>
+        <v>360.876</v>
       </c>
       <c r="G35">
         <v>73.8</v>
@@ -4157,28 +4157,28 @@
         <v>107.1</v>
       </c>
       <c r="M35">
-        <v>19.3694886</v>
+        <v>19.9564428</v>
       </c>
       <c r="N35">
-        <v>87.73051139999998</v>
+        <v>87.14355719999999</v>
       </c>
       <c r="O35">
-        <v>17.54610228</v>
+        <v>17.42871144</v>
       </c>
       <c r="P35">
-        <v>70.18440911999998</v>
+        <v>69.71484575999999</v>
       </c>
       <c r="Q35">
-        <v>184.08440912</v>
+        <v>183.61484576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1136209950529938</v>
+        <v>0.1145011585083568</v>
       </c>
       <c r="T35">
-        <v>0.7426676940234204</v>
+        <v>0.7523058446174561</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.529314800804806</v>
+        <v>5.366687894898783</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09061236461551547</v>
+        <v>0.0904994625455251</v>
       </c>
       <c r="C36">
-        <v>817.7972917514644</v>
+        <v>809.0414735099769</v>
       </c>
       <c r="D36">
-        <v>1104.873291751464</v>
+        <v>1106.731473509977</v>
       </c>
       <c r="E36">
-        <v>55.37600000000003</v>
+        <v>65.99000000000007</v>
       </c>
       <c r="F36">
-        <v>360.876</v>
+        <v>371.4900000000001</v>
       </c>
       <c r="G36">
         <v>73.8</v>
@@ -4239,28 +4239,28 @@
         <v>107.1</v>
       </c>
       <c r="M36">
-        <v>19.9564428</v>
+        <v>20.54339700000001</v>
       </c>
       <c r="N36">
-        <v>87.14355719999999</v>
+        <v>86.556603</v>
       </c>
       <c r="O36">
-        <v>17.42871144</v>
+        <v>17.3113206</v>
       </c>
       <c r="P36">
-        <v>69.71484575999999</v>
+        <v>69.24528239999999</v>
       </c>
       <c r="Q36">
-        <v>183.61484576</v>
+        <v>183.1452824</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1145011585083568</v>
+        <v>0.1154084039161925</v>
       </c>
       <c r="T36">
-        <v>0.7523058446174561</v>
+        <v>0.7622405536913083</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.366687894898783</v>
+        <v>5.213353955044532</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0904994625455251</v>
+        <v>0.09038656047553474</v>
       </c>
       <c r="C37">
-        <v>809.0414735099769</v>
+        <v>800.2919159976784</v>
       </c>
       <c r="D37">
-        <v>1106.731473509977</v>
+        <v>1108.595915997679</v>
       </c>
       <c r="E37">
-        <v>65.99000000000007</v>
+        <v>76.6040000000001</v>
       </c>
       <c r="F37">
-        <v>371.4900000000001</v>
+        <v>382.1040000000001</v>
       </c>
       <c r="G37">
         <v>73.8</v>
@@ -4321,28 +4321,28 @@
         <v>107.1</v>
       </c>
       <c r="M37">
-        <v>20.54339700000001</v>
+        <v>21.13035120000001</v>
       </c>
       <c r="N37">
-        <v>86.556603</v>
+        <v>85.96964879999999</v>
       </c>
       <c r="O37">
-        <v>17.3113206</v>
+        <v>17.19392976</v>
       </c>
       <c r="P37">
-        <v>69.24528239999999</v>
+        <v>68.77571903999998</v>
       </c>
       <c r="Q37">
-        <v>183.1452824</v>
+        <v>182.67571904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1154084039161925</v>
+        <v>0.116344000743023</v>
       </c>
       <c r="T37">
-        <v>0.7622405536913083</v>
+        <v>0.7724857224237184</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.213353955044532</v>
+        <v>5.068538567404405</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09038656047553476</v>
+        <v>0.09027365840554437</v>
       </c>
       <c r="C38">
-        <v>800.2919159976782</v>
+        <v>791.5486509091602</v>
       </c>
       <c r="D38">
-        <v>1108.595915997678</v>
+        <v>1110.46665090916</v>
       </c>
       <c r="E38">
-        <v>76.60400000000004</v>
+        <v>87.21800000000002</v>
       </c>
       <c r="F38">
-        <v>382.104</v>
+        <v>392.718</v>
       </c>
       <c r="G38">
         <v>73.8</v>
@@ -4403,28 +4403,28 @@
         <v>107.1</v>
       </c>
       <c r="M38">
-        <v>21.1303512</v>
+        <v>21.7173054</v>
       </c>
       <c r="N38">
-        <v>85.96964879999999</v>
+        <v>85.38269459999999</v>
       </c>
       <c r="O38">
-        <v>17.19392976</v>
+        <v>17.07653892</v>
       </c>
       <c r="P38">
-        <v>68.77571903999998</v>
+        <v>68.30615567999999</v>
       </c>
       <c r="Q38">
-        <v>182.67571904</v>
+        <v>182.20615568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.116344000743023</v>
+        <v>0.1173092990564196</v>
       </c>
       <c r="T38">
-        <v>0.7724857224237183</v>
+        <v>0.783056134607951</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.068538567404406</v>
+        <v>4.931551038555639</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09027365840554437</v>
+        <v>0.09016075633555398</v>
       </c>
       <c r="C39">
-        <v>791.5486509091602</v>
+        <v>782.811710153311</v>
       </c>
       <c r="D39">
-        <v>1110.46665090916</v>
+        <v>1112.343710153311</v>
       </c>
       <c r="E39">
-        <v>87.21800000000002</v>
+        <v>97.83200000000005</v>
       </c>
       <c r="F39">
-        <v>392.718</v>
+        <v>403.3320000000001</v>
       </c>
       <c r="G39">
         <v>73.8</v>
@@ -4485,28 +4485,28 @@
         <v>107.1</v>
       </c>
       <c r="M39">
-        <v>21.7173054</v>
+        <v>22.30425960000001</v>
       </c>
       <c r="N39">
-        <v>85.38269459999999</v>
+        <v>84.79574039999999</v>
       </c>
       <c r="O39">
-        <v>17.07653892</v>
+        <v>16.95914808</v>
       </c>
       <c r="P39">
-        <v>68.30615567999999</v>
+        <v>67.83659231999999</v>
       </c>
       <c r="Q39">
-        <v>182.20615568</v>
+        <v>181.73659232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1173092990564196</v>
+        <v>0.1183057360250871</v>
       </c>
       <c r="T39">
-        <v>0.783056134607951</v>
+        <v>0.7939675278303845</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.931551038555639</v>
+        <v>4.80177337964628</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09016075633555398</v>
+        <v>0.09004785426556361</v>
       </c>
       <c r="C40">
-        <v>782.811710153311</v>
+        <v>774.0811258551313</v>
       </c>
       <c r="D40">
-        <v>1112.343710153311</v>
+        <v>1114.227125855131</v>
       </c>
       <c r="E40">
-        <v>97.83200000000005</v>
+        <v>108.446</v>
       </c>
       <c r="F40">
-        <v>403.3320000000001</v>
+        <v>413.946</v>
       </c>
       <c r="G40">
         <v>73.8</v>
@@ -4567,28 +4567,28 @@
         <v>107.1</v>
       </c>
       <c r="M40">
-        <v>22.30425960000001</v>
+        <v>22.8912138</v>
       </c>
       <c r="N40">
-        <v>84.79574039999999</v>
+        <v>84.20878619999999</v>
       </c>
       <c r="O40">
-        <v>16.95914808</v>
+        <v>16.84175724</v>
       </c>
       <c r="P40">
-        <v>67.83659231999999</v>
+        <v>67.36702896</v>
       </c>
       <c r="Q40">
-        <v>181.73659232</v>
+        <v>181.26702896</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1183057360250871</v>
+        <v>0.119334843058301</v>
       </c>
       <c r="T40">
-        <v>0.7939675278303845</v>
+        <v>0.805236671650275</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.80177337964628</v>
+        <v>4.678650985296375</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09004785426556361</v>
+        <v>0.08993495219557324</v>
       </c>
       <c r="C41">
-        <v>774.0811258551313</v>
+        <v>765.3569303575658</v>
       </c>
       <c r="D41">
-        <v>1114.227125855131</v>
+        <v>1116.116930357566</v>
       </c>
       <c r="E41">
-        <v>108.446</v>
+        <v>119.0600000000001</v>
       </c>
       <c r="F41">
-        <v>413.946</v>
+        <v>424.5600000000001</v>
       </c>
       <c r="G41">
         <v>73.8</v>
@@ -4649,28 +4649,28 @@
         <v>107.1</v>
       </c>
       <c r="M41">
-        <v>22.8912138</v>
+        <v>23.478168</v>
       </c>
       <c r="N41">
-        <v>84.20878619999999</v>
+        <v>83.62183199999998</v>
       </c>
       <c r="O41">
-        <v>16.84175724</v>
+        <v>16.7243664</v>
       </c>
       <c r="P41">
-        <v>67.36702896</v>
+        <v>66.89746559999999</v>
       </c>
       <c r="Q41">
-        <v>181.26702896</v>
+        <v>180.7974656</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.119334843058301</v>
+        <v>0.1203982536592887</v>
       </c>
       <c r="T41">
-        <v>0.805236671650275</v>
+        <v>0.8168814535974952</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.678650985296375</v>
+        <v>4.561684710663966</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08993495219557324</v>
+        <v>0.09064205012558285</v>
       </c>
       <c r="C42">
-        <v>765.3569303575658</v>
+        <v>743.0117527786086</v>
       </c>
       <c r="D42">
-        <v>1116.116930357566</v>
+        <v>1104.385752778609</v>
       </c>
       <c r="E42">
-        <v>119.0600000000001</v>
+        <v>129.6740000000001</v>
       </c>
       <c r="F42">
-        <v>424.5600000000001</v>
+        <v>435.1740000000001</v>
       </c>
       <c r="G42">
         <v>73.8</v>
@@ -4731,45 +4731,45 @@
         <v>107.1</v>
       </c>
       <c r="M42">
-        <v>23.478168</v>
+        <v>25.15305720000001</v>
       </c>
       <c r="N42">
-        <v>83.62183199999998</v>
+        <v>81.94694279999999</v>
       </c>
       <c r="O42">
-        <v>16.7243664</v>
+        <v>16.38938856</v>
       </c>
       <c r="P42">
-        <v>66.89746559999999</v>
+        <v>65.55755423999999</v>
       </c>
       <c r="Q42">
-        <v>180.7974656</v>
+        <v>179.45755424</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1203982536592887</v>
+        <v>0.1214977120772591</v>
       </c>
       <c r="T42">
-        <v>0.8168814535974952</v>
+        <v>0.8289209739158077</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.561684710663966</v>
+        <v>4.257931715751832</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09064205012558285</v>
+        <v>0.09054914805559248</v>
       </c>
       <c r="C43">
-        <v>743.0117527786086</v>
+        <v>733.9249625227555</v>
       </c>
       <c r="D43">
-        <v>1104.385752778609</v>
+        <v>1105.912962522756</v>
       </c>
       <c r="E43">
-        <v>129.6740000000001</v>
+        <v>140.2880000000001</v>
       </c>
       <c r="F43">
-        <v>435.1740000000001</v>
+        <v>445.7880000000001</v>
       </c>
       <c r="G43">
         <v>73.8</v>
@@ -4813,28 +4813,28 @@
         <v>107.1</v>
       </c>
       <c r="M43">
-        <v>25.15305720000001</v>
+        <v>25.76654640000001</v>
       </c>
       <c r="N43">
-        <v>81.94694279999999</v>
+        <v>81.33345359999998</v>
       </c>
       <c r="O43">
-        <v>16.38938856</v>
+        <v>16.26669072</v>
       </c>
       <c r="P43">
-        <v>65.55755423999999</v>
+        <v>65.06676287999998</v>
       </c>
       <c r="Q43">
-        <v>179.45755424</v>
+        <v>178.96676288</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1214977120772591</v>
+        <v>0.1226350828544698</v>
       </c>
       <c r="T43">
-        <v>0.8289209739158077</v>
+        <v>0.8413756501071653</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.257931715751832</v>
+        <v>4.156552389186312</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09054914805559248</v>
+        <v>0.09045624598560212</v>
       </c>
       <c r="C44">
-        <v>733.9249625227555</v>
+        <v>724.8424019473396</v>
       </c>
       <c r="D44">
-        <v>1105.912962522756</v>
+        <v>1107.44440194734</v>
       </c>
       <c r="E44">
-        <v>140.288</v>
+        <v>150.902</v>
       </c>
       <c r="F44">
-        <v>445.788</v>
+        <v>456.402</v>
       </c>
       <c r="G44">
         <v>73.8</v>
@@ -4895,28 +4895,28 @@
         <v>107.1</v>
       </c>
       <c r="M44">
-        <v>25.7665464</v>
+        <v>26.3800356</v>
       </c>
       <c r="N44">
-        <v>81.33345359999998</v>
+        <v>80.71996439999999</v>
       </c>
       <c r="O44">
-        <v>16.26669072</v>
+        <v>16.14399288</v>
       </c>
       <c r="P44">
-        <v>65.06676287999998</v>
+        <v>64.57597152</v>
       </c>
       <c r="Q44">
-        <v>178.96676288</v>
+        <v>178.47597152</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1226350828544698</v>
+        <v>0.1238123613782493</v>
       </c>
       <c r="T44">
-        <v>0.8413756501071651</v>
+        <v>0.8542673324806758</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.156552389186313</v>
+        <v>4.059888380135469</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09045624598560212</v>
+        <v>0.09159534391561173</v>
       </c>
       <c r="C45">
-        <v>724.8424019473396</v>
+        <v>695.7389323495281</v>
       </c>
       <c r="D45">
-        <v>1107.44440194734</v>
+        <v>1088.954932349528</v>
       </c>
       <c r="E45">
-        <v>150.902</v>
+        <v>161.516</v>
       </c>
       <c r="F45">
-        <v>456.402</v>
+        <v>467.016</v>
       </c>
       <c r="G45">
         <v>73.8</v>
@@ -4977,45 +4977,45 @@
         <v>107.1</v>
       </c>
       <c r="M45">
-        <v>26.3800356</v>
+        <v>28.6280808</v>
       </c>
       <c r="N45">
-        <v>80.71996439999999</v>
+        <v>78.47191919999999</v>
       </c>
       <c r="O45">
-        <v>16.14399288</v>
+        <v>15.69438384</v>
       </c>
       <c r="P45">
-        <v>64.57597152</v>
+        <v>62.77753535999999</v>
       </c>
       <c r="Q45">
-        <v>178.47597152</v>
+        <v>176.67753536</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1238123613782493</v>
+        <v>0.1250316855635924</v>
       </c>
       <c r="T45">
-        <v>0.8542673324806758</v>
+        <v>0.8676194320818117</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.059888380135469</v>
+        <v>3.741082077706026</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09159534391561173</v>
+        <v>0.09153044184562135</v>
       </c>
       <c r="C46">
-        <v>695.7389323495281</v>
+        <v>686.1617997902476</v>
       </c>
       <c r="D46">
-        <v>1088.954932349528</v>
+        <v>1089.991799790248</v>
       </c>
       <c r="E46">
-        <v>161.516</v>
+        <v>172.1300000000001</v>
       </c>
       <c r="F46">
-        <v>467.016</v>
+        <v>477.6300000000001</v>
       </c>
       <c r="G46">
         <v>73.8</v>
@@ -5059,28 +5059,28 @@
         <v>107.1</v>
       </c>
       <c r="M46">
-        <v>28.6280808</v>
+        <v>29.278719</v>
       </c>
       <c r="N46">
-        <v>78.47191919999999</v>
+        <v>77.821281</v>
       </c>
       <c r="O46">
-        <v>15.69438384</v>
+        <v>15.5642562</v>
       </c>
       <c r="P46">
-        <v>62.77753535999999</v>
+        <v>62.2570248</v>
       </c>
       <c r="Q46">
-        <v>176.67753536</v>
+        <v>176.1570248</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1250316855635924</v>
+        <v>0.1262953488102206</v>
       </c>
       <c r="T46">
-        <v>0.8676194320818117</v>
+        <v>0.8814570625775343</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.741082077706026</v>
+        <v>3.65794692042367</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09153044184562135</v>
+        <v>0.09146553977563099</v>
       </c>
       <c r="C47">
-        <v>686.1617997902476</v>
+        <v>676.5866436557076</v>
       </c>
       <c r="D47">
-        <v>1089.991799790248</v>
+        <v>1091.030643655708</v>
       </c>
       <c r="E47">
-        <v>172.1300000000001</v>
+        <v>182.7440000000001</v>
       </c>
       <c r="F47">
-        <v>477.6300000000001</v>
+        <v>488.2440000000001</v>
       </c>
       <c r="G47">
         <v>73.8</v>
@@ -5141,28 +5141,28 @@
         <v>107.1</v>
       </c>
       <c r="M47">
-        <v>29.278719</v>
+        <v>29.92935720000001</v>
       </c>
       <c r="N47">
-        <v>77.821281</v>
+        <v>77.1706428</v>
       </c>
       <c r="O47">
-        <v>15.5642562</v>
+        <v>15.43412856</v>
       </c>
       <c r="P47">
-        <v>62.2570248</v>
+        <v>61.73651424</v>
       </c>
       <c r="Q47">
-        <v>176.1570248</v>
+        <v>175.63651424</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1262953488102206</v>
+        <v>0.1276058143993166</v>
       </c>
       <c r="T47">
-        <v>0.8814570625775343</v>
+        <v>0.8958071979064319</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.65794692042367</v>
+        <v>3.578426335197068</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09146553977563099</v>
+        <v>0.09140063770564061</v>
       </c>
       <c r="C48">
-        <v>676.5866436557076</v>
+        <v>667.0134696023421</v>
       </c>
       <c r="D48">
-        <v>1091.030643655708</v>
+        <v>1092.071469602342</v>
       </c>
       <c r="E48">
-        <v>182.7440000000001</v>
+        <v>193.3580000000001</v>
       </c>
       <c r="F48">
-        <v>488.2440000000001</v>
+        <v>498.8580000000001</v>
       </c>
       <c r="G48">
         <v>73.8</v>
@@ -5223,28 +5223,28 @@
         <v>107.1</v>
       </c>
       <c r="M48">
-        <v>29.92935720000001</v>
+        <v>30.5799954</v>
       </c>
       <c r="N48">
-        <v>77.1706428</v>
+        <v>76.52000459999999</v>
       </c>
       <c r="O48">
-        <v>15.43412856</v>
+        <v>15.30400092</v>
       </c>
       <c r="P48">
-        <v>61.73651424</v>
+        <v>61.21600367999999</v>
       </c>
       <c r="Q48">
-        <v>175.63651424</v>
+        <v>175.11600368</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1276058143993166</v>
+        <v>0.1289657315200766</v>
       </c>
       <c r="T48">
-        <v>0.8958071979064319</v>
+        <v>0.9106988477760427</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.578426335197068</v>
+        <v>3.50228960466096</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09140063770564061</v>
+        <v>0.09241093563565024</v>
       </c>
       <c r="C49">
-        <v>667.0134696023421</v>
+        <v>640.4193068134927</v>
       </c>
       <c r="D49">
-        <v>1092.071469602342</v>
+        <v>1076.091306813493</v>
       </c>
       <c r="E49">
-        <v>193.3580000000001</v>
+        <v>203.9720000000001</v>
       </c>
       <c r="F49">
-        <v>498.8580000000001</v>
+        <v>509.4720000000001</v>
       </c>
       <c r="G49">
         <v>73.8</v>
@@ -5305,45 +5305,45 @@
         <v>107.1</v>
       </c>
       <c r="M49">
-        <v>30.5799954</v>
+        <v>32.65715520000001</v>
       </c>
       <c r="N49">
-        <v>76.52000459999999</v>
+        <v>74.44284479999999</v>
       </c>
       <c r="O49">
-        <v>15.30400092</v>
+        <v>14.88856896</v>
       </c>
       <c r="P49">
-        <v>61.21600367999999</v>
+        <v>59.55427583999999</v>
       </c>
       <c r="Q49">
-        <v>175.11600368</v>
+        <v>173.45427584</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1289657315200766</v>
+        <v>0.1303779531454812</v>
       </c>
       <c r="T49">
-        <v>0.9106988477760427</v>
+        <v>0.9261632534098692</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.50228960466096</v>
+        <v>3.279526319549107</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09241093563565023</v>
+        <v>0.09236843356565985</v>
       </c>
       <c r="C50">
-        <v>640.419306813493</v>
+        <v>630.4681446772004</v>
       </c>
       <c r="D50">
-        <v>1076.091306813493</v>
+        <v>1076.7541446772</v>
       </c>
       <c r="E50">
-        <v>203.972</v>
+        <v>214.586</v>
       </c>
       <c r="F50">
-        <v>509.472</v>
+        <v>520.086</v>
       </c>
       <c r="G50">
         <v>73.8</v>
@@ -5387,28 +5387,28 @@
         <v>107.1</v>
       </c>
       <c r="M50">
-        <v>32.65715520000001</v>
+        <v>33.3375126</v>
       </c>
       <c r="N50">
-        <v>74.44284479999999</v>
+        <v>73.7624874</v>
       </c>
       <c r="O50">
-        <v>14.88856896</v>
+        <v>14.75249748</v>
       </c>
       <c r="P50">
-        <v>59.55427583999999</v>
+        <v>59.00998992</v>
       </c>
       <c r="Q50">
-        <v>173.45427584</v>
+        <v>172.90998992</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1303779531454812</v>
+        <v>0.1318455560110977</v>
       </c>
       <c r="T50">
-        <v>0.9261632534098692</v>
+        <v>0.9422341063234535</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.279526319549107</v>
+        <v>3.212597210986881</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09236843356565985</v>
+        <v>0.09232593149566948</v>
       </c>
       <c r="C51">
-        <v>630.4681446772004</v>
+        <v>620.5177996180939</v>
       </c>
       <c r="D51">
-        <v>1076.7541446772</v>
+        <v>1077.417799618094</v>
       </c>
       <c r="E51">
-        <v>214.586</v>
+        <v>225.2</v>
       </c>
       <c r="F51">
-        <v>520.086</v>
+        <v>530.7</v>
       </c>
       <c r="G51">
         <v>73.8</v>
@@ -5469,28 +5469,28 @@
         <v>107.1</v>
       </c>
       <c r="M51">
-        <v>33.3375126</v>
+        <v>34.01787</v>
       </c>
       <c r="N51">
-        <v>73.7624874</v>
+        <v>73.08212999999999</v>
       </c>
       <c r="O51">
-        <v>14.75249748</v>
+        <v>14.616426</v>
       </c>
       <c r="P51">
-        <v>59.00998992</v>
+        <v>58.465704</v>
       </c>
       <c r="Q51">
-        <v>172.90998992</v>
+        <v>172.365704</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1318455560110977</v>
+        <v>0.1333718629913389</v>
       </c>
       <c r="T51">
-        <v>0.9422341063234535</v>
+        <v>0.9589477933535814</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.212597210986881</v>
+        <v>3.148345266767143</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09232593149566948</v>
+        <v>0.09228342942567909</v>
       </c>
       <c r="C52">
-        <v>620.5177996180939</v>
+        <v>610.5682731479162</v>
       </c>
       <c r="D52">
-        <v>1077.417799618094</v>
+        <v>1078.082273147916</v>
       </c>
       <c r="E52">
-        <v>225.2</v>
+        <v>235.8140000000001</v>
       </c>
       <c r="F52">
-        <v>530.7</v>
+        <v>541.3140000000001</v>
       </c>
       <c r="G52">
         <v>73.8</v>
@@ -5551,28 +5551,28 @@
         <v>107.1</v>
       </c>
       <c r="M52">
-        <v>34.01787</v>
+        <v>34.69822740000001</v>
       </c>
       <c r="N52">
-        <v>73.08212999999999</v>
+        <v>72.40177259999999</v>
       </c>
       <c r="O52">
-        <v>14.616426</v>
+        <v>14.48035452</v>
       </c>
       <c r="P52">
-        <v>58.465704</v>
+        <v>57.92141807999999</v>
       </c>
       <c r="Q52">
-        <v>172.365704</v>
+        <v>171.82141808</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1333718629913389</v>
+        <v>0.1349604682156716</v>
       </c>
       <c r="T52">
-        <v>0.9589477933535814</v>
+        <v>0.9763436716910614</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.148345266767143</v>
+        <v>3.086613006634453</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09228342942567909</v>
+        <v>0.0922409273556887</v>
       </c>
       <c r="C53">
-        <v>610.5682731479162</v>
+        <v>600.6195667821414</v>
       </c>
       <c r="D53">
-        <v>1078.082273147916</v>
+        <v>1078.747566782142</v>
       </c>
       <c r="E53">
-        <v>235.8140000000001</v>
+        <v>246.4280000000001</v>
       </c>
       <c r="F53">
-        <v>541.3140000000001</v>
+        <v>551.9280000000001</v>
       </c>
       <c r="G53">
         <v>73.8</v>
@@ -5633,28 +5633,28 @@
         <v>107.1</v>
       </c>
       <c r="M53">
-        <v>34.69822740000001</v>
+        <v>35.37858480000001</v>
       </c>
       <c r="N53">
-        <v>72.40177259999999</v>
+        <v>71.72141519999998</v>
       </c>
       <c r="O53">
-        <v>14.48035452</v>
+        <v>14.34428304</v>
       </c>
       <c r="P53">
-        <v>57.92141807999999</v>
+        <v>57.37713215999999</v>
       </c>
       <c r="Q53">
-        <v>171.82141808</v>
+        <v>171.27713216</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1349604682156716</v>
+        <v>0.1366152653243515</v>
       </c>
       <c r="T53">
-        <v>0.9763436716910614</v>
+        <v>0.9944643782926028</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.086613006634453</v>
+        <v>3.027255064199175</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0922409273556887</v>
+        <v>0.09550562528569834</v>
       </c>
       <c r="C54">
-        <v>600.6195667821414</v>
+        <v>541.1852134536372</v>
       </c>
       <c r="D54">
-        <v>1078.747566782142</v>
+        <v>1029.927213453637</v>
       </c>
       <c r="E54">
-        <v>246.4280000000001</v>
+        <v>257.042</v>
       </c>
       <c r="F54">
-        <v>551.9280000000001</v>
+        <v>562.542</v>
       </c>
       <c r="G54">
         <v>73.8</v>
@@ -5715,45 +5715,45 @@
         <v>107.1</v>
       </c>
       <c r="M54">
-        <v>35.37858480000001</v>
+        <v>40.44676980000001</v>
       </c>
       <c r="N54">
-        <v>71.72141519999998</v>
+        <v>66.6532302</v>
       </c>
       <c r="O54">
-        <v>14.34428304</v>
+        <v>13.33064604</v>
       </c>
       <c r="P54">
-        <v>57.37713215999999</v>
+        <v>53.32258416</v>
       </c>
       <c r="Q54">
-        <v>171.27713216</v>
+        <v>167.22258416</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1366152653243515</v>
+        <v>0.1383404793312731</v>
       </c>
       <c r="T54">
-        <v>0.9944643782926028</v>
+        <v>1.013356178792082</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.027255064199175</v>
+        <v>2.647924680501927</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09550562528569834</v>
+        <v>0.09552552321570795</v>
       </c>
       <c r="C55">
-        <v>541.1852134536372</v>
+        <v>530.287204035879</v>
       </c>
       <c r="D55">
-        <v>1029.927213453637</v>
+        <v>1029.643204035879</v>
       </c>
       <c r="E55">
-        <v>257.042</v>
+        <v>267.6560000000001</v>
       </c>
       <c r="F55">
-        <v>562.542</v>
+        <v>573.1560000000001</v>
       </c>
       <c r="G55">
         <v>73.8</v>
@@ -5797,28 +5797,28 @@
         <v>107.1</v>
       </c>
       <c r="M55">
-        <v>40.44676980000001</v>
+        <v>41.2099164</v>
       </c>
       <c r="N55">
-        <v>66.6532302</v>
+        <v>65.8900836</v>
       </c>
       <c r="O55">
-        <v>13.33064604</v>
+        <v>13.17801672</v>
       </c>
       <c r="P55">
-        <v>53.32258416</v>
+        <v>52.71206687999999</v>
       </c>
       <c r="Q55">
-        <v>167.22258416</v>
+        <v>166.61206688</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1383404793312731</v>
+        <v>0.1401407026428434</v>
       </c>
       <c r="T55">
-        <v>1.013356178792082</v>
+        <v>1.033069361921974</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.647924680501927</v>
+        <v>2.59888903827041</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09552552321570795</v>
+        <v>0.0955454211457176</v>
       </c>
       <c r="C56">
-        <v>530.287204035879</v>
+        <v>519.3893512099875</v>
       </c>
       <c r="D56">
-        <v>1029.643204035879</v>
+        <v>1029.359351209988</v>
       </c>
       <c r="E56">
-        <v>267.6560000000001</v>
+        <v>278.2700000000001</v>
       </c>
       <c r="F56">
-        <v>573.1560000000001</v>
+        <v>583.7700000000001</v>
       </c>
       <c r="G56">
         <v>73.8</v>
@@ -5879,28 +5879,28 @@
         <v>107.1</v>
       </c>
       <c r="M56">
-        <v>41.2099164</v>
+        <v>41.97306300000001</v>
       </c>
       <c r="N56">
-        <v>65.8900836</v>
+        <v>65.12693699999998</v>
       </c>
       <c r="O56">
-        <v>13.17801672</v>
+        <v>13.0253874</v>
       </c>
       <c r="P56">
-        <v>52.71206687999999</v>
+        <v>52.10154959999998</v>
       </c>
       <c r="Q56">
-        <v>166.61206688</v>
+        <v>166.0015496</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1401407026428434</v>
+        <v>0.1420209358793724</v>
       </c>
       <c r="T56">
-        <v>1.033069361921974</v>
+        <v>1.053658686524306</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.59888903827041</v>
+        <v>2.551636510301856</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0955454211457176</v>
+        <v>0.09556531907572721</v>
       </c>
       <c r="C57">
-        <v>519.3893512099875</v>
+        <v>508.4916548464909</v>
       </c>
       <c r="D57">
-        <v>1029.359351209988</v>
+        <v>1029.075654846491</v>
       </c>
       <c r="E57">
-        <v>278.2700000000001</v>
+        <v>288.8840000000001</v>
       </c>
       <c r="F57">
-        <v>583.7700000000001</v>
+        <v>594.3840000000001</v>
       </c>
       <c r="G57">
         <v>73.8</v>
@@ -5961,28 +5961,28 @@
         <v>107.1</v>
       </c>
       <c r="M57">
-        <v>41.97306300000001</v>
+        <v>42.73620960000001</v>
       </c>
       <c r="N57">
-        <v>65.12693699999998</v>
+        <v>64.36379039999998</v>
       </c>
       <c r="O57">
-        <v>13.0253874</v>
+        <v>12.87275808</v>
       </c>
       <c r="P57">
-        <v>52.10154959999998</v>
+        <v>51.49103231999999</v>
       </c>
       <c r="Q57">
-        <v>166.0015496</v>
+        <v>165.39103232</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1420209358793724</v>
+        <v>0.1439866342630164</v>
       </c>
       <c r="T57">
-        <v>1.053658686524306</v>
+        <v>1.075183889517652</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.551636510301856</v>
+        <v>2.506071572617895</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09556531907572721</v>
+        <v>0.09736361700573684</v>
       </c>
       <c r="C58">
-        <v>508.4916548464909</v>
+        <v>472.8682773893028</v>
       </c>
       <c r="D58">
-        <v>1029.075654846491</v>
+        <v>1004.066277389303</v>
       </c>
       <c r="E58">
-        <v>288.8840000000001</v>
+        <v>299.4980000000002</v>
       </c>
       <c r="F58">
-        <v>594.3840000000001</v>
+        <v>604.9980000000002</v>
       </c>
       <c r="G58">
         <v>73.8</v>
@@ -6043,45 +6043,45 @@
         <v>107.1</v>
       </c>
       <c r="M58">
-        <v>42.73620960000001</v>
+        <v>45.85884840000001</v>
       </c>
       <c r="N58">
-        <v>64.36379039999998</v>
+        <v>61.24115159999998</v>
       </c>
       <c r="O58">
-        <v>12.87275808</v>
+        <v>12.24823032</v>
       </c>
       <c r="P58">
-        <v>51.49103231999999</v>
+        <v>48.99292127999998</v>
       </c>
       <c r="Q58">
-        <v>165.39103232</v>
+        <v>162.89292128</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1439866342630164</v>
+        <v>0.1460437604784578</v>
       </c>
       <c r="T58">
-        <v>1.075183889517652</v>
+        <v>1.097710264743247</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.506071572617895</v>
+        <v>2.335427158262438</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09736361700573684</v>
+        <v>0.09741471493574645</v>
       </c>
       <c r="C59">
-        <v>472.8682773893028</v>
+        <v>461.5613945249161</v>
       </c>
       <c r="D59">
-        <v>1004.066277389303</v>
+        <v>1003.373394524916</v>
       </c>
       <c r="E59">
-        <v>299.4980000000002</v>
+        <v>310.1120000000001</v>
       </c>
       <c r="F59">
-        <v>604.9980000000002</v>
+        <v>615.6120000000001</v>
       </c>
       <c r="G59">
         <v>73.8</v>
@@ -6125,28 +6125,28 @@
         <v>107.1</v>
       </c>
       <c r="M59">
-        <v>45.85884840000001</v>
+        <v>46.66338960000001</v>
       </c>
       <c r="N59">
-        <v>61.24115159999998</v>
+        <v>60.43661039999999</v>
       </c>
       <c r="O59">
-        <v>12.24823032</v>
+        <v>12.08732208</v>
       </c>
       <c r="P59">
-        <v>48.99292127999998</v>
+        <v>48.34928831999999</v>
       </c>
       <c r="Q59">
-        <v>162.89292128</v>
+        <v>162.24928832</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1460437604784578</v>
+        <v>0.1481988450851106</v>
       </c>
       <c r="T59">
-        <v>1.097710264743247</v>
+        <v>1.121309324503394</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.335427158262438</v>
+        <v>2.295161172775155</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09741471493574645</v>
+        <v>0.09746581286575609</v>
       </c>
       <c r="C60">
-        <v>461.5613945249162</v>
+        <v>450.2554672858827</v>
       </c>
       <c r="D60">
-        <v>1003.373394524916</v>
+        <v>1002.681467285883</v>
       </c>
       <c r="E60">
-        <v>310.112</v>
+        <v>320.726</v>
       </c>
       <c r="F60">
-        <v>615.612</v>
+        <v>626.226</v>
       </c>
       <c r="G60">
         <v>73.8</v>
@@ -6207,28 +6207,28 @@
         <v>107.1</v>
       </c>
       <c r="M60">
-        <v>46.6633896</v>
+        <v>47.4679308</v>
       </c>
       <c r="N60">
-        <v>60.43661039999999</v>
+        <v>59.63206919999999</v>
       </c>
       <c r="O60">
-        <v>12.08732208</v>
+        <v>11.92641384</v>
       </c>
       <c r="P60">
-        <v>48.34928831999999</v>
+        <v>47.70565535999999</v>
       </c>
       <c r="Q60">
-        <v>162.24928832</v>
+        <v>161.60565536</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1481988450851106</v>
+        <v>0.1504590557701368</v>
       </c>
       <c r="T60">
-        <v>1.121309324503394</v>
+        <v>1.146059557910378</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.295161172775155</v>
+        <v>2.256260135948458</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09746581286575609</v>
+        <v>0.09751691079576572</v>
       </c>
       <c r="C61">
-        <v>450.2554672858827</v>
+        <v>438.9504936965644</v>
       </c>
       <c r="D61">
-        <v>1002.681467285883</v>
+        <v>1001.990493696564</v>
       </c>
       <c r="E61">
-        <v>320.726</v>
+        <v>331.34</v>
       </c>
       <c r="F61">
-        <v>626.226</v>
+        <v>636.84</v>
       </c>
       <c r="G61">
         <v>73.8</v>
@@ -6289,28 +6289,28 @@
         <v>107.1</v>
       </c>
       <c r="M61">
-        <v>47.4679308</v>
+        <v>48.27247200000001</v>
       </c>
       <c r="N61">
-        <v>59.63206919999999</v>
+        <v>58.82752799999999</v>
       </c>
       <c r="O61">
-        <v>11.92641384</v>
+        <v>11.7655056</v>
       </c>
       <c r="P61">
-        <v>47.70565535999999</v>
+        <v>47.06202239999999</v>
       </c>
       <c r="Q61">
-        <v>161.60565536</v>
+        <v>160.9620224</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1504590557701368</v>
+        <v>0.1528322769894143</v>
       </c>
       <c r="T61">
-        <v>1.146059557910378</v>
+        <v>1.172047302987711</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.256260135948458</v>
+        <v>2.218655800349317</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09751691079576572</v>
+        <v>0.09756800872577531</v>
       </c>
       <c r="C62">
-        <v>438.9504936965644</v>
+        <v>427.646471786766</v>
       </c>
       <c r="D62">
-        <v>1001.990493696564</v>
+        <v>1001.300471786766</v>
       </c>
       <c r="E62">
-        <v>331.34</v>
+        <v>341.9540000000001</v>
       </c>
       <c r="F62">
-        <v>636.84</v>
+        <v>647.4540000000001</v>
       </c>
       <c r="G62">
         <v>73.8</v>
@@ -6371,28 +6371,28 @@
         <v>107.1</v>
       </c>
       <c r="M62">
-        <v>48.27247200000001</v>
+        <v>49.07701320000001</v>
       </c>
       <c r="N62">
-        <v>58.82752799999999</v>
+        <v>58.02298679999998</v>
       </c>
       <c r="O62">
-        <v>11.7655056</v>
+        <v>11.60459736</v>
       </c>
       <c r="P62">
-        <v>47.06202239999999</v>
+        <v>46.41838943999998</v>
       </c>
       <c r="Q62">
-        <v>160.9620224</v>
+        <v>160.31838944</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1528322769894143</v>
+        <v>0.1553272018609624</v>
       </c>
       <c r="T62">
-        <v>1.172047302987711</v>
+        <v>1.199367752940804</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.218655800349317</v>
+        <v>2.182284393786213</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09756800872577531</v>
+        <v>0.09761910665578497</v>
       </c>
       <c r="C63">
-        <v>427.646471786766</v>
+        <v>416.3433995917136</v>
       </c>
       <c r="D63">
-        <v>1001.300471786766</v>
+        <v>1000.611399591714</v>
       </c>
       <c r="E63">
-        <v>341.9540000000001</v>
+        <v>352.5680000000001</v>
       </c>
       <c r="F63">
-        <v>647.4540000000001</v>
+        <v>658.0680000000001</v>
       </c>
       <c r="G63">
         <v>73.8</v>
@@ -6453,28 +6453,28 @@
         <v>107.1</v>
       </c>
       <c r="M63">
-        <v>49.07701320000001</v>
+        <v>49.88155440000001</v>
       </c>
       <c r="N63">
-        <v>58.02298679999998</v>
+        <v>57.21844559999998</v>
       </c>
       <c r="O63">
-        <v>11.60459736</v>
+        <v>11.44368912</v>
       </c>
       <c r="P63">
-        <v>46.41838943999998</v>
+        <v>45.77475647999999</v>
       </c>
       <c r="Q63">
-        <v>160.31838944</v>
+        <v>159.67475648</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1553272018609624</v>
+        <v>0.1579534385678551</v>
       </c>
       <c r="T63">
-        <v>1.199367752940804</v>
+        <v>1.228126121312481</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.182284393786213</v>
+        <v>2.147086258402564</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09761910665578497</v>
+        <v>0.09767020458579458</v>
       </c>
       <c r="C64">
-        <v>416.3433995917136</v>
+        <v>405.041275152041</v>
       </c>
       <c r="D64">
-        <v>1000.611399591714</v>
+        <v>999.9232751520409</v>
       </c>
       <c r="E64">
-        <v>352.5680000000001</v>
+        <v>363.182</v>
       </c>
       <c r="F64">
-        <v>658.0680000000001</v>
+        <v>668.682</v>
       </c>
       <c r="G64">
         <v>73.8</v>
@@ -6535,28 +6535,28 @@
         <v>107.1</v>
       </c>
       <c r="M64">
-        <v>49.88155440000001</v>
+        <v>50.68609560000001</v>
       </c>
       <c r="N64">
-        <v>57.21844559999998</v>
+        <v>56.41390439999999</v>
       </c>
       <c r="O64">
-        <v>11.44368912</v>
+        <v>11.28278088</v>
       </c>
       <c r="P64">
-        <v>45.77475647999999</v>
+        <v>45.13112351999999</v>
       </c>
       <c r="Q64">
-        <v>159.67475648</v>
+        <v>159.03112352</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1579534385678551</v>
+        <v>0.160721634015661</v>
       </c>
       <c r="T64">
-        <v>1.228126121312481</v>
+        <v>1.258438996082628</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.147086258402564</v>
+        <v>2.113005524142206</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09767020458579458</v>
+        <v>0.0977213025158042</v>
       </c>
       <c r="C65">
-        <v>405.041275152041</v>
+        <v>393.7400965137651</v>
       </c>
       <c r="D65">
-        <v>999.9232751520409</v>
+        <v>999.2360965137651</v>
       </c>
       <c r="E65">
-        <v>363.182</v>
+        <v>373.796</v>
       </c>
       <c r="F65">
-        <v>668.682</v>
+        <v>679.296</v>
       </c>
       <c r="G65">
         <v>73.8</v>
@@ -6617,28 +6617,28 @@
         <v>107.1</v>
       </c>
       <c r="M65">
-        <v>50.68609560000001</v>
+        <v>51.49063680000001</v>
       </c>
       <c r="N65">
-        <v>56.41390439999999</v>
+        <v>55.60936319999998</v>
       </c>
       <c r="O65">
-        <v>11.28278088</v>
+        <v>11.12187264</v>
       </c>
       <c r="P65">
-        <v>45.13112351999999</v>
+        <v>44.48749055999998</v>
       </c>
       <c r="Q65">
-        <v>159.03112352</v>
+        <v>158.38749056</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.160721634015661</v>
+        <v>0.1636436180994561</v>
       </c>
       <c r="T65">
-        <v>1.258438996082628</v>
+        <v>1.290435919451116</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.113005524142206</v>
+        <v>2.079989812827484</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0977213025158042</v>
+        <v>0.09777240044581381</v>
       </c>
       <c r="C66">
-        <v>393.7400965137651</v>
+        <v>382.4398617282729</v>
       </c>
       <c r="D66">
-        <v>999.2360965137651</v>
+        <v>998.549861728273</v>
       </c>
       <c r="E66">
-        <v>373.796</v>
+        <v>384.4100000000001</v>
       </c>
       <c r="F66">
-        <v>679.296</v>
+        <v>689.9100000000001</v>
       </c>
       <c r="G66">
         <v>73.8</v>
@@ -6699,28 +6699,28 @@
         <v>107.1</v>
       </c>
       <c r="M66">
-        <v>51.49063680000001</v>
+        <v>52.29517800000001</v>
       </c>
       <c r="N66">
-        <v>55.60936319999998</v>
+        <v>54.80482199999999</v>
       </c>
       <c r="O66">
-        <v>11.12187264</v>
+        <v>10.9609644</v>
       </c>
       <c r="P66">
-        <v>44.48749055999998</v>
+        <v>43.84385759999999</v>
       </c>
       <c r="Q66">
-        <v>158.38749056</v>
+        <v>157.7438576</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1636436180994561</v>
+        <v>0.1667325727023252</v>
       </c>
       <c r="T66">
-        <v>1.290435919451116</v>
+        <v>1.32426123844066</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.079989812827484</v>
+        <v>2.047989969553215</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09777240044581381</v>
+        <v>0.09782349837582344</v>
       </c>
       <c r="C67">
-        <v>382.4398617282729</v>
+        <v>371.1405688522989</v>
       </c>
       <c r="D67">
-        <v>998.549861728273</v>
+        <v>997.8645688522989</v>
       </c>
       <c r="E67">
-        <v>384.4100000000001</v>
+        <v>395.0240000000001</v>
       </c>
       <c r="F67">
-        <v>689.9100000000001</v>
+        <v>700.5240000000001</v>
       </c>
       <c r="G67">
         <v>73.8</v>
@@ -6781,28 +6781,28 @@
         <v>107.1</v>
       </c>
       <c r="M67">
-        <v>52.29517800000001</v>
+        <v>53.09971920000001</v>
       </c>
       <c r="N67">
-        <v>54.80482199999999</v>
+        <v>54.00028079999998</v>
       </c>
       <c r="O67">
-        <v>10.9609644</v>
+        <v>10.80005616</v>
       </c>
       <c r="P67">
-        <v>43.84385759999999</v>
+        <v>43.20022463999999</v>
       </c>
       <c r="Q67">
-        <v>157.7438576</v>
+        <v>157.10022464</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1667325727023252</v>
+        <v>0.1700032305171278</v>
       </c>
       <c r="T67">
-        <v>1.32426123844066</v>
+        <v>1.360076282076648</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.047989969553215</v>
+        <v>2.016959818499378</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09782349837582344</v>
+        <v>0.1054857963058331</v>
       </c>
       <c r="C68">
-        <v>371.1405688522989</v>
+        <v>267.4172206683387</v>
       </c>
       <c r="D68">
-        <v>997.8645688522989</v>
+        <v>904.7552206683389</v>
       </c>
       <c r="E68">
-        <v>395.0240000000001</v>
+        <v>405.6380000000001</v>
       </c>
       <c r="F68">
-        <v>700.5240000000001</v>
+        <v>711.1380000000001</v>
       </c>
       <c r="G68">
         <v>73.8</v>
@@ -6863,45 +6863,45 @@
         <v>107.1</v>
       </c>
       <c r="M68">
-        <v>53.09971920000001</v>
+        <v>64.00242000000001</v>
       </c>
       <c r="N68">
-        <v>54.00028079999998</v>
+        <v>43.09757999999998</v>
       </c>
       <c r="O68">
-        <v>10.80005616</v>
+        <v>8.619515999999996</v>
       </c>
       <c r="P68">
-        <v>43.20022463999999</v>
+        <v>34.47806399999998</v>
       </c>
       <c r="Q68">
-        <v>157.10022464</v>
+        <v>148.378064</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1700032305171278</v>
+        <v>0.173472110017676</v>
       </c>
       <c r="T68">
-        <v>1.360076282076648</v>
+        <v>1.398061934417848</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.016959818499378</v>
+        <v>1.673374225537096</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1054857963058331</v>
+        <v>0.1056504942358427</v>
       </c>
       <c r="C69">
-        <v>267.4172206683387</v>
+        <v>254.9922487067344</v>
       </c>
       <c r="D69">
-        <v>904.7552206683389</v>
+        <v>902.9442487067345</v>
       </c>
       <c r="E69">
-        <v>405.6380000000001</v>
+        <v>416.2520000000001</v>
       </c>
       <c r="F69">
-        <v>711.1380000000001</v>
+        <v>721.7520000000001</v>
       </c>
       <c r="G69">
         <v>73.8</v>
@@ -6945,28 +6945,28 @@
         <v>107.1</v>
       </c>
       <c r="M69">
-        <v>64.00242000000001</v>
+        <v>64.95768000000001</v>
       </c>
       <c r="N69">
-        <v>43.09757999999998</v>
+        <v>42.14231999999998</v>
       </c>
       <c r="O69">
-        <v>8.619515999999996</v>
+        <v>8.428463999999996</v>
       </c>
       <c r="P69">
-        <v>34.47806399999998</v>
+        <v>33.71385599999999</v>
       </c>
       <c r="Q69">
-        <v>148.378064</v>
+        <v>147.613856</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.173472110017676</v>
+        <v>0.1771577944870084</v>
       </c>
       <c r="T69">
-        <v>1.398061934417848</v>
+        <v>1.438421690030372</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.673374225537096</v>
+        <v>1.648765781043904</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1056504942358427</v>
+        <v>0.1058151921658523</v>
       </c>
       <c r="C70">
-        <v>254.9922487067344</v>
+        <v>242.5745120015788</v>
       </c>
       <c r="D70">
-        <v>902.9442487067345</v>
+        <v>901.1405120015789</v>
       </c>
       <c r="E70">
-        <v>416.2520000000001</v>
+        <v>426.8660000000001</v>
       </c>
       <c r="F70">
-        <v>721.7520000000001</v>
+        <v>732.3660000000001</v>
       </c>
       <c r="G70">
         <v>73.8</v>
@@ -7027,28 +7027,28 @@
         <v>107.1</v>
       </c>
       <c r="M70">
-        <v>64.95768000000001</v>
+        <v>65.91294000000001</v>
       </c>
       <c r="N70">
-        <v>42.14231999999998</v>
+        <v>41.18705999999999</v>
       </c>
       <c r="O70">
-        <v>8.428463999999996</v>
+        <v>8.237411999999997</v>
       </c>
       <c r="P70">
-        <v>33.71385599999999</v>
+        <v>32.94964799999999</v>
       </c>
       <c r="Q70">
-        <v>147.613856</v>
+        <v>146.849648</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1771577944870084</v>
+        <v>0.1810812650511365</v>
       </c>
       <c r="T70">
-        <v>1.438421690030372</v>
+        <v>1.481385300843705</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.648765781043904</v>
+        <v>1.624870624796891</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1058151921658523</v>
+        <v>0.1059798900958619</v>
       </c>
       <c r="C71">
-        <v>242.5745120015788</v>
+        <v>230.1639672795035</v>
       </c>
       <c r="D71">
-        <v>901.1405120015789</v>
+        <v>899.3439672795037</v>
       </c>
       <c r="E71">
-        <v>426.8660000000001</v>
+        <v>437.4800000000001</v>
       </c>
       <c r="F71">
-        <v>732.3660000000001</v>
+        <v>742.9800000000001</v>
       </c>
       <c r="G71">
         <v>73.8</v>
@@ -7109,28 +7109,28 @@
         <v>107.1</v>
       </c>
       <c r="M71">
-        <v>65.91294000000001</v>
+        <v>66.86820000000002</v>
       </c>
       <c r="N71">
-        <v>41.18705999999999</v>
+        <v>40.23179999999998</v>
       </c>
       <c r="O71">
-        <v>8.237411999999997</v>
+        <v>8.046359999999996</v>
       </c>
       <c r="P71">
-        <v>32.94964799999999</v>
+        <v>32.18543999999999</v>
       </c>
       <c r="Q71">
-        <v>146.849648</v>
+        <v>146.08544</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1810812650511365</v>
+        <v>0.1852663003195398</v>
       </c>
       <c r="T71">
-        <v>1.481385300843705</v>
+        <v>1.527213152377926</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.624870624796891</v>
+        <v>1.601658187299792</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1059798900958619</v>
+        <v>0.1061445880258716</v>
       </c>
       <c r="C72">
-        <v>230.1639672795035</v>
+        <v>217.7605716115384</v>
       </c>
       <c r="D72">
-        <v>899.3439672795037</v>
+        <v>897.5545716115386</v>
       </c>
       <c r="E72">
-        <v>437.4800000000001</v>
+        <v>448.0940000000002</v>
       </c>
       <c r="F72">
-        <v>742.9800000000001</v>
+        <v>753.5940000000002</v>
       </c>
       <c r="G72">
         <v>73.8</v>
@@ -7191,28 +7191,28 @@
         <v>107.1</v>
       </c>
       <c r="M72">
-        <v>66.86820000000002</v>
+        <v>67.82346000000001</v>
       </c>
       <c r="N72">
-        <v>40.23179999999998</v>
+        <v>39.27653999999998</v>
       </c>
       <c r="O72">
-        <v>8.046359999999996</v>
+        <v>7.855307999999997</v>
       </c>
       <c r="P72">
-        <v>32.18543999999999</v>
+        <v>31.42123199999999</v>
       </c>
       <c r="Q72">
-        <v>146.08544</v>
+        <v>145.321232</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1852663003195398</v>
+        <v>0.189739958709902</v>
       </c>
       <c r="T72">
-        <v>1.527213152377926</v>
+        <v>1.576201545397266</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.601658187299792</v>
+        <v>1.579099621281485</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1061445880258716</v>
+        <v>0.1063092859558812</v>
       </c>
       <c r="C73">
-        <v>217.7605716115386</v>
+        <v>205.3642824096933</v>
       </c>
       <c r="D73">
-        <v>897.5545716115387</v>
+        <v>895.7722824096934</v>
       </c>
       <c r="E73">
-        <v>448.0940000000001</v>
+        <v>458.7080000000001</v>
       </c>
       <c r="F73">
-        <v>753.5940000000001</v>
+        <v>764.2080000000001</v>
       </c>
       <c r="G73">
         <v>73.8</v>
@@ -7273,28 +7273,28 @@
         <v>107.1</v>
       </c>
       <c r="M73">
-        <v>67.82346</v>
+        <v>68.77872000000001</v>
       </c>
       <c r="N73">
-        <v>39.27654</v>
+        <v>38.32127999999999</v>
       </c>
       <c r="O73">
-        <v>7.855308</v>
+        <v>7.664255999999998</v>
       </c>
       <c r="P73">
-        <v>31.421232</v>
+        <v>30.65702399999999</v>
       </c>
       <c r="Q73">
-        <v>145.321232</v>
+        <v>144.557024</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1897399587099019</v>
+        <v>0.1945331641281471</v>
       </c>
       <c r="T73">
-        <v>1.576201545397266</v>
+        <v>1.628689109346559</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.579099621281486</v>
+        <v>1.55716768209702</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1063092859558812</v>
+        <v>0.1064739838858908</v>
       </c>
       <c r="C74">
-        <v>205.3642824096933</v>
+        <v>192.9750574235773</v>
       </c>
       <c r="D74">
-        <v>895.7722824096934</v>
+        <v>893.9970574235773</v>
       </c>
       <c r="E74">
-        <v>458.7080000000001</v>
+        <v>469.322</v>
       </c>
       <c r="F74">
-        <v>764.2080000000001</v>
+        <v>774.822</v>
       </c>
       <c r="G74">
         <v>73.8</v>
@@ -7355,28 +7355,28 @@
         <v>107.1</v>
       </c>
       <c r="M74">
-        <v>68.77872000000001</v>
+        <v>69.73398</v>
       </c>
       <c r="N74">
-        <v>38.32127999999999</v>
+        <v>37.36601999999999</v>
       </c>
       <c r="O74">
-        <v>7.664255999999998</v>
+        <v>7.473203999999999</v>
       </c>
       <c r="P74">
-        <v>30.65702399999999</v>
+        <v>29.89281599999999</v>
       </c>
       <c r="Q74">
-        <v>144.557024</v>
+        <v>143.792816</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1945331641281471</v>
+        <v>0.1996814217995956</v>
       </c>
       <c r="T74">
-        <v>1.628689109346559</v>
+        <v>1.685064640995799</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.55716768209702</v>
+        <v>1.535836617958705</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1064739838858908</v>
+        <v>0.1066386818159004</v>
       </c>
       <c r="C75">
-        <v>192.9750574235773</v>
+        <v>180.5928547370619</v>
       </c>
       <c r="D75">
-        <v>893.9970574235773</v>
+        <v>892.228854737062</v>
       </c>
       <c r="E75">
-        <v>469.322</v>
+        <v>479.936</v>
       </c>
       <c r="F75">
-        <v>774.822</v>
+        <v>785.436</v>
       </c>
       <c r="G75">
         <v>73.8</v>
@@ -7437,28 +7437,28 @@
         <v>107.1</v>
       </c>
       <c r="M75">
-        <v>69.73398</v>
+        <v>70.68924</v>
       </c>
       <c r="N75">
-        <v>37.36601999999999</v>
+        <v>36.41076</v>
       </c>
       <c r="O75">
-        <v>7.473203999999999</v>
+        <v>7.282152</v>
       </c>
       <c r="P75">
-        <v>29.89281599999999</v>
+        <v>29.128608</v>
       </c>
       <c r="Q75">
-        <v>143.792816</v>
+        <v>143.028608</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1996814217995956</v>
+        <v>0.2052256992919247</v>
       </c>
       <c r="T75">
-        <v>1.685064640995799</v>
+        <v>1.745776752002674</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.535836617958705</v>
+        <v>1.515082069067371</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1066386818159004</v>
+        <v>0.1433319855725392</v>
       </c>
       <c r="C76">
-        <v>180.5928547370619</v>
+        <v>-102.9265586094383</v>
       </c>
       <c r="D76">
-        <v>892.228854737062</v>
+        <v>619.3234413905618</v>
       </c>
       <c r="E76">
-        <v>479.936</v>
+        <v>490.5500000000001</v>
       </c>
       <c r="F76">
-        <v>785.436</v>
+        <v>796.0500000000001</v>
       </c>
       <c r="G76">
         <v>73.8</v>
@@ -7519,45 +7519,45 @@
         <v>107.1</v>
       </c>
       <c r="M76">
-        <v>70.68924</v>
+        <v>116.86014</v>
       </c>
       <c r="N76">
-        <v>36.41076</v>
+        <v>-9.760140000000021</v>
       </c>
       <c r="O76">
-        <v>7.282152</v>
+        <v>-1.952028000000004</v>
       </c>
       <c r="P76">
-        <v>29.128608</v>
+        <v>-7.808112000000017</v>
       </c>
       <c r="Q76">
-        <v>143.028608</v>
+        <v>106.091888</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2052256992919247</v>
+        <v>0.2136515149300661</v>
       </c>
       <c r="T76">
-        <v>1.745776752002674</v>
+        <v>1.838042886779307</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2</v>
+        <v>0.1832960323340362</v>
       </c>
       <c r="W76">
-        <v>0.07199999999999999</v>
+        <v>0.1198921424533635</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.515082069067371</v>
+        <v>0.916480161670181</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1433319855725392</v>
+        <v>0.1443419855725391</v>
       </c>
       <c r="C77">
-        <v>-102.9265586094383</v>
+        <v>-118.7112290637506</v>
       </c>
       <c r="D77">
-        <v>619.3234413905618</v>
+        <v>614.1527709362496</v>
       </c>
       <c r="E77">
-        <v>490.5500000000001</v>
+        <v>501.1640000000001</v>
       </c>
       <c r="F77">
-        <v>796.0500000000001</v>
+        <v>806.6640000000001</v>
       </c>
       <c r="G77">
         <v>73.8</v>
@@ -7601,37 +7601,37 @@
         <v>107.1</v>
       </c>
       <c r="M77">
-        <v>116.86014</v>
+        <v>118.4182752</v>
       </c>
       <c r="N77">
-        <v>-9.760140000000021</v>
+        <v>-11.31827520000003</v>
       </c>
       <c r="O77">
-        <v>-1.952028000000004</v>
+        <v>-2.263655040000006</v>
       </c>
       <c r="P77">
-        <v>-7.808112000000017</v>
+        <v>-9.054620160000024</v>
       </c>
       <c r="Q77">
-        <v>106.091888</v>
+        <v>104.84537984</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2136515149300661</v>
+        <v>0.2206453280521522</v>
       </c>
       <c r="T77">
-        <v>1.838042886779307</v>
+        <v>1.914628007061778</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1832960323340362</v>
+        <v>0.1808842424349041</v>
       </c>
       <c r="W77">
-        <v>0.1198921424533635</v>
+        <v>0.1202461932105561</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.916480161670181</v>
+        <v>0.9044212121745207</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1443419855725391</v>
+        <v>0.1453519855725391</v>
       </c>
       <c r="C78">
-        <v>-118.7112290637506</v>
+        <v>-134.4102755467876</v>
       </c>
       <c r="D78">
-        <v>614.1527709362496</v>
+        <v>609.0677244532126</v>
       </c>
       <c r="E78">
-        <v>501.1640000000001</v>
+        <v>511.7780000000001</v>
       </c>
       <c r="F78">
-        <v>806.6640000000001</v>
+        <v>817.2780000000001</v>
       </c>
       <c r="G78">
         <v>73.8</v>
@@ -7683,37 +7683,37 @@
         <v>107.1</v>
       </c>
       <c r="M78">
-        <v>118.4182752</v>
+        <v>119.9764104</v>
       </c>
       <c r="N78">
-        <v>-11.31827520000003</v>
+        <v>-12.87641040000004</v>
       </c>
       <c r="O78">
-        <v>-2.263655040000006</v>
+        <v>-2.575282080000008</v>
       </c>
       <c r="P78">
-        <v>-9.054620160000024</v>
+        <v>-10.30112832000003</v>
       </c>
       <c r="Q78">
-        <v>104.84537984</v>
+        <v>103.59887168</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2206453280521522</v>
+        <v>0.2282472988370284</v>
       </c>
       <c r="T78">
-        <v>1.914628007061778</v>
+        <v>1.997872703020986</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1808842424349041</v>
+        <v>0.178535096429256</v>
       </c>
       <c r="W78">
-        <v>0.1202461932105561</v>
+        <v>0.1205910478441852</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9044212121745207</v>
+        <v>0.89267548214628</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1453519855725391</v>
+        <v>0.1463619855725392</v>
       </c>
       <c r="C79">
-        <v>-134.4102755467876</v>
+        <v>-150.0258074349234</v>
       </c>
       <c r="D79">
-        <v>609.0677244532126</v>
+        <v>604.0661925650767</v>
       </c>
       <c r="E79">
-        <v>511.7780000000001</v>
+        <v>522.3920000000001</v>
       </c>
       <c r="F79">
-        <v>817.2780000000001</v>
+        <v>827.8920000000001</v>
       </c>
       <c r="G79">
         <v>73.8</v>
@@ -7765,37 +7765,37 @@
         <v>107.1</v>
       </c>
       <c r="M79">
-        <v>119.9764104</v>
+        <v>121.5345456</v>
       </c>
       <c r="N79">
-        <v>-12.87641040000004</v>
+        <v>-14.43454560000002</v>
       </c>
       <c r="O79">
-        <v>-2.575282080000008</v>
+        <v>-2.886909120000004</v>
       </c>
       <c r="P79">
-        <v>-10.30112832000003</v>
+        <v>-11.54763648000002</v>
       </c>
       <c r="Q79">
-        <v>103.59887168</v>
+        <v>102.35236352</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2282472988370284</v>
+        <v>0.2365403578750751</v>
       </c>
       <c r="T79">
-        <v>1.997872703020986</v>
+        <v>2.088685098612849</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.178535096429256</v>
+        <v>0.1762461849365733</v>
       </c>
       <c r="W79">
-        <v>0.1205910478441852</v>
+        <v>0.1209270600513111</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.89267548214628</v>
+        <v>0.8812309246828663</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1463619855725392</v>
+        <v>0.1473719855725392</v>
       </c>
       <c r="C80">
-        <v>-150.0258074349234</v>
+        <v>-165.5598653819046</v>
       </c>
       <c r="D80">
-        <v>604.0661925650767</v>
+        <v>599.1461346180955</v>
       </c>
       <c r="E80">
-        <v>522.3920000000001</v>
+        <v>533.0060000000001</v>
       </c>
       <c r="F80">
-        <v>827.8920000000001</v>
+        <v>838.5060000000001</v>
       </c>
       <c r="G80">
         <v>73.8</v>
@@ -7847,37 +7847,37 @@
         <v>107.1</v>
       </c>
       <c r="M80">
-        <v>121.5345456</v>
+        <v>123.0926808</v>
       </c>
       <c r="N80">
-        <v>-14.43454560000002</v>
+        <v>-15.99268080000003</v>
       </c>
       <c r="O80">
-        <v>-2.886909120000004</v>
+        <v>-3.198536160000006</v>
       </c>
       <c r="P80">
-        <v>-11.54763648000002</v>
+        <v>-12.79414464000002</v>
       </c>
       <c r="Q80">
-        <v>102.35236352</v>
+        <v>101.10585536</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2365403578750751</v>
+        <v>0.2456232320596025</v>
       </c>
       <c r="T80">
-        <v>2.088685098612849</v>
+        <v>2.18814629378489</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1762461849365733</v>
+        <v>0.1740152205702875</v>
       </c>
       <c r="W80">
-        <v>0.1209270600513111</v>
+        <v>0.1212545656202818</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8812309246828663</v>
+        <v>0.8700761028514375</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1473719855725392</v>
+        <v>0.1483819855725392</v>
       </c>
       <c r="C81">
-        <v>-165.5598653819046</v>
+        <v>-181.0144240949335</v>
       </c>
       <c r="D81">
-        <v>599.1461346180955</v>
+        <v>594.3055759050667</v>
       </c>
       <c r="E81">
-        <v>533.0060000000001</v>
+        <v>543.6200000000001</v>
       </c>
       <c r="F81">
-        <v>838.5060000000001</v>
+        <v>849.1200000000001</v>
       </c>
       <c r="G81">
         <v>73.8</v>
@@ -7929,37 +7929,37 @@
         <v>107.1</v>
       </c>
       <c r="M81">
-        <v>123.0926808</v>
+        <v>124.650816</v>
       </c>
       <c r="N81">
-        <v>-15.99268080000003</v>
+        <v>-17.55081600000004</v>
       </c>
       <c r="O81">
-        <v>-3.198536160000006</v>
+        <v>-3.510163200000008</v>
       </c>
       <c r="P81">
-        <v>-12.79414464000002</v>
+        <v>-14.04065280000003</v>
       </c>
       <c r="Q81">
-        <v>101.10585536</v>
+        <v>99.85934719999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2456232320596025</v>
+        <v>0.2556143936625827</v>
       </c>
       <c r="T81">
-        <v>2.18814629378489</v>
+        <v>2.297553608474135</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1740152205702875</v>
+        <v>0.1718400303131589</v>
       </c>
       <c r="W81">
-        <v>0.1212545656202818</v>
+        <v>0.1215738835500283</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8700761028514375</v>
+        <v>0.8592001515657945</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1483819855725392</v>
+        <v>0.1493919855725391</v>
       </c>
       <c r="C82">
-        <v>-181.0144240949335</v>
+        <v>-196.3913949772596</v>
       </c>
       <c r="D82">
-        <v>594.3055759050667</v>
+        <v>589.5426050227406</v>
       </c>
       <c r="E82">
-        <v>543.6200000000001</v>
+        <v>554.2340000000002</v>
       </c>
       <c r="F82">
-        <v>849.1200000000001</v>
+        <v>859.7340000000002</v>
       </c>
       <c r="G82">
         <v>73.8</v>
@@ -8011,37 +8011,37 @@
         <v>107.1</v>
       </c>
       <c r="M82">
-        <v>124.650816</v>
+        <v>126.2089512</v>
       </c>
       <c r="N82">
-        <v>-17.55081600000004</v>
+        <v>-19.10895120000004</v>
       </c>
       <c r="O82">
-        <v>-3.510163200000008</v>
+        <v>-3.821790240000007</v>
       </c>
       <c r="P82">
-        <v>-14.04065280000003</v>
+        <v>-15.28716096000003</v>
       </c>
       <c r="Q82">
-        <v>99.85934719999997</v>
+        <v>98.61283903999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2556143936625827</v>
+        <v>0.2666572564869291</v>
       </c>
       <c r="T82">
-        <v>2.297553608474135</v>
+        <v>2.418477482604352</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1718400303131589</v>
+        <v>0.1697185484574409</v>
       </c>
       <c r="W82">
-        <v>0.1215738835500283</v>
+        <v>0.1218853170864477</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8592001515657945</v>
+        <v>0.8485927422872045</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1493919855725391</v>
+        <v>0.1504019855725391</v>
       </c>
       <c r="C83">
-        <v>-196.3913949772596</v>
+        <v>-211.692628644713</v>
       </c>
       <c r="D83">
-        <v>589.5426050227406</v>
+        <v>584.8553713552873</v>
       </c>
       <c r="E83">
-        <v>554.2340000000002</v>
+        <v>564.8480000000002</v>
       </c>
       <c r="F83">
-        <v>859.7340000000002</v>
+        <v>870.3480000000002</v>
       </c>
       <c r="G83">
         <v>73.8</v>
@@ -8093,37 +8093,37 @@
         <v>107.1</v>
       </c>
       <c r="M83">
-        <v>126.2089512</v>
+        <v>127.7670864</v>
       </c>
       <c r="N83">
-        <v>-19.10895120000004</v>
+        <v>-20.66708640000004</v>
       </c>
       <c r="O83">
-        <v>-3.821790240000007</v>
+        <v>-4.13341728000001</v>
       </c>
       <c r="P83">
-        <v>-15.28716096000003</v>
+        <v>-16.53366912000003</v>
       </c>
       <c r="Q83">
-        <v>98.61283903999998</v>
+        <v>97.36633087999996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2666572564869291</v>
+        <v>0.2789271040695363</v>
       </c>
       <c r="T83">
-        <v>2.418477482604352</v>
+        <v>2.552837342749039</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1697185484574409</v>
+        <v>0.1676488100616185</v>
       </c>
       <c r="W83">
-        <v>0.1218853170864477</v>
+        <v>0.1221891546829544</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8485927422872045</v>
+        <v>0.8382440503080921</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1504019855725391</v>
+        <v>0.1514119855725391</v>
       </c>
       <c r="C84">
-        <v>-211.692628644713</v>
+        <v>-226.9199173231304</v>
       </c>
       <c r="D84">
-        <v>584.8553713552873</v>
+        <v>580.2420826768697</v>
       </c>
       <c r="E84">
-        <v>564.8480000000002</v>
+        <v>575.4620000000001</v>
       </c>
       <c r="F84">
-        <v>870.3480000000002</v>
+        <v>880.9620000000001</v>
       </c>
       <c r="G84">
         <v>73.8</v>
@@ -8175,37 +8175,37 @@
         <v>107.1</v>
       </c>
       <c r="M84">
-        <v>127.7670864</v>
+        <v>129.3252216</v>
       </c>
       <c r="N84">
-        <v>-20.66708640000004</v>
+        <v>-22.22522160000003</v>
       </c>
       <c r="O84">
-        <v>-4.13341728000001</v>
+        <v>-4.445044320000005</v>
       </c>
       <c r="P84">
-        <v>-16.53366912000003</v>
+        <v>-17.78017728000002</v>
       </c>
       <c r="Q84">
-        <v>97.36633087999996</v>
+        <v>96.11982271999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2789271040695363</v>
+        <v>0.2926404631324502</v>
       </c>
       <c r="T84">
-        <v>2.552837342749039</v>
+        <v>2.703004245263688</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1676488100616185</v>
+        <v>0.1656289448801532</v>
       </c>
       <c r="W84">
-        <v>0.1221891546829544</v>
+        <v>0.1224856708915935</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8382440503080921</v>
+        <v>0.8281447244007659</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1514119855725391</v>
+        <v>0.1524219855725392</v>
       </c>
       <c r="C85">
-        <v>-226.9199173231304</v>
+        <v>-242.0749971332118</v>
       </c>
       <c r="D85">
-        <v>580.2420826768697</v>
+        <v>575.7010028667884</v>
       </c>
       <c r="E85">
-        <v>575.4620000000001</v>
+        <v>586.0760000000001</v>
       </c>
       <c r="F85">
-        <v>880.9620000000001</v>
+        <v>891.5760000000001</v>
       </c>
       <c r="G85">
         <v>73.8</v>
@@ -8257,37 +8257,37 @@
         <v>107.1</v>
       </c>
       <c r="M85">
-        <v>129.3252216</v>
+        <v>130.8833568</v>
       </c>
       <c r="N85">
-        <v>-22.22522160000003</v>
+        <v>-23.78335680000004</v>
       </c>
       <c r="O85">
-        <v>-4.445044320000005</v>
+        <v>-4.756671360000007</v>
       </c>
       <c r="P85">
-        <v>-17.78017728000002</v>
+        <v>-19.02668544000003</v>
       </c>
       <c r="Q85">
-        <v>96.11982271999999</v>
+        <v>94.87331455999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2926404631324502</v>
+        <v>0.3080679920782284</v>
       </c>
       <c r="T85">
-        <v>2.703004245263688</v>
+        <v>2.871942010592669</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1656289448801532</v>
+        <v>0.163657171726818</v>
       </c>
       <c r="W85">
-        <v>0.1224856708915935</v>
+        <v>0.1227751271905031</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8281447244007659</v>
+        <v>0.8182858586340901</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1524219855725391</v>
+        <v>0.1534319855725391</v>
       </c>
       <c r="C86">
-        <v>-242.0749971332115</v>
+        <v>-257.1595502689138</v>
       </c>
       <c r="D86">
-        <v>575.7010028667886</v>
+        <v>571.2304497310863</v>
       </c>
       <c r="E86">
-        <v>586.076</v>
+        <v>596.6900000000001</v>
       </c>
       <c r="F86">
-        <v>891.576</v>
+        <v>902.1900000000001</v>
       </c>
       <c r="G86">
         <v>73.8</v>
@@ -8339,37 +8339,37 @@
         <v>107.1</v>
       </c>
       <c r="M86">
-        <v>130.8833568</v>
+        <v>132.441492</v>
       </c>
       <c r="N86">
-        <v>-23.78335680000001</v>
+        <v>-25.34149200000002</v>
       </c>
       <c r="O86">
-        <v>-4.756671360000001</v>
+        <v>-5.068298400000003</v>
       </c>
       <c r="P86">
-        <v>-19.02668544</v>
+        <v>-20.27319360000001</v>
       </c>
       <c r="Q86">
-        <v>94.87331456</v>
+        <v>93.62680639999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3080679920782282</v>
+        <v>0.3255525248834435</v>
       </c>
       <c r="T86">
-        <v>2.871942010592667</v>
+        <v>3.063404811298845</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.163657171726818</v>
+        <v>0.1617317932359143</v>
       </c>
       <c r="W86">
-        <v>0.1227751271905031</v>
+        <v>0.1230577727529678</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8182858586340902</v>
+        <v>0.8086589661795714</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1534319855725391</v>
+        <v>0.202680593332421</v>
       </c>
       <c r="C87">
-        <v>-257.1595502689138</v>
+        <v>-424.6632696636651</v>
       </c>
       <c r="D87">
-        <v>571.2304497310863</v>
+        <v>414.340730336335</v>
       </c>
       <c r="E87">
-        <v>596.6900000000001</v>
+        <v>607.3040000000001</v>
       </c>
       <c r="F87">
-        <v>902.1900000000001</v>
+        <v>912.8040000000001</v>
       </c>
       <c r="G87">
         <v>73.8</v>
@@ -8421,45 +8421,45 @@
         <v>107.1</v>
       </c>
       <c r="M87">
-        <v>132.441492</v>
+        <v>183.2910432</v>
       </c>
       <c r="N87">
-        <v>-25.34149200000002</v>
+        <v>-76.19104320000002</v>
       </c>
       <c r="O87">
-        <v>-5.068298400000003</v>
+        <v>-15.23820864000001</v>
       </c>
       <c r="P87">
-        <v>-20.27319360000001</v>
+        <v>-60.95283456000002</v>
       </c>
       <c r="Q87">
-        <v>93.62680639999999</v>
+        <v>52.94716543999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3255525248834435</v>
+        <v>0.3583820463742741</v>
       </c>
       <c r="T87">
-        <v>3.063404811298845</v>
+        <v>3.422901527653956</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1617317932359143</v>
+        <v>0.1168633209023058</v>
       </c>
       <c r="W87">
-        <v>0.1230577727529678</v>
+        <v>0.177333845162817</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8086589661795714</v>
+        <v>0.5843166045115291</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.202680593332421</v>
+        <v>0.204230593332421</v>
       </c>
       <c r="C88">
-        <v>-424.6632696636651</v>
+        <v>-438.8281868379504</v>
       </c>
       <c r="D88">
-        <v>414.340730336335</v>
+        <v>410.7898131620497</v>
       </c>
       <c r="E88">
-        <v>607.3040000000001</v>
+        <v>617.9180000000001</v>
       </c>
       <c r="F88">
-        <v>912.8040000000001</v>
+        <v>923.4180000000001</v>
       </c>
       <c r="G88">
         <v>73.8</v>
@@ -8503,37 +8503,37 @@
         <v>107.1</v>
       </c>
       <c r="M88">
-        <v>183.2910432</v>
+        <v>185.4223344</v>
       </c>
       <c r="N88">
-        <v>-76.19104320000002</v>
+        <v>-78.32233440000005</v>
       </c>
       <c r="O88">
-        <v>-15.23820864000001</v>
+        <v>-15.66446688000001</v>
       </c>
       <c r="P88">
-        <v>-60.95283456000002</v>
+        <v>-62.65786752000004</v>
       </c>
       <c r="Q88">
-        <v>52.94716543999998</v>
+        <v>51.24213247999997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3583820463742741</v>
+        <v>0.3824268191722952</v>
       </c>
       <c r="T88">
-        <v>3.422901527653956</v>
+        <v>3.686201645165799</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1168633209023058</v>
+        <v>0.1155200643402103</v>
       </c>
       <c r="W88">
-        <v>0.177333845162817</v>
+        <v>0.1776035710804858</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5843166045115291</v>
+        <v>0.5776003217010517</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.204230593332421</v>
+        <v>0.205780593332421</v>
       </c>
       <c r="C89">
-        <v>-438.8281868379504</v>
+        <v>-452.9327581649149</v>
       </c>
       <c r="D89">
-        <v>410.7898131620497</v>
+        <v>407.2992418350851</v>
       </c>
       <c r="E89">
-        <v>617.9180000000001</v>
+        <v>628.532</v>
       </c>
       <c r="F89">
-        <v>923.4180000000001</v>
+        <v>934.032</v>
       </c>
       <c r="G89">
         <v>73.8</v>
@@ -8585,37 +8585,37 @@
         <v>107.1</v>
       </c>
       <c r="M89">
-        <v>185.4223344</v>
+        <v>187.5536256</v>
       </c>
       <c r="N89">
-        <v>-78.32233440000005</v>
+        <v>-80.45362560000001</v>
       </c>
       <c r="O89">
-        <v>-15.66446688000001</v>
+        <v>-16.09072512</v>
       </c>
       <c r="P89">
-        <v>-62.65786752000004</v>
+        <v>-64.36290048000001</v>
       </c>
       <c r="Q89">
-        <v>51.24213247999997</v>
+        <v>49.53709952</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3824268191722952</v>
+        <v>0.4104790541033198</v>
       </c>
       <c r="T89">
-        <v>3.686201645165799</v>
+        <v>3.993385115596283</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1155200643402103</v>
+        <v>0.1142073363363443</v>
       </c>
       <c r="W89">
-        <v>0.1776035710804858</v>
+        <v>0.1778671668636621</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5776003217010517</v>
+        <v>0.5710366816817216</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.205780593332421</v>
+        <v>0.207330593332421</v>
       </c>
       <c r="C90">
-        <v>-452.9327581649149</v>
+        <v>-466.9785089990694</v>
       </c>
       <c r="D90">
-        <v>407.2992418350851</v>
+        <v>403.8674910009307</v>
       </c>
       <c r="E90">
-        <v>628.532</v>
+        <v>639.1460000000001</v>
       </c>
       <c r="F90">
-        <v>934.032</v>
+        <v>944.6460000000001</v>
       </c>
       <c r="G90">
         <v>73.8</v>
@@ -8667,37 +8667,37 @@
         <v>107.1</v>
       </c>
       <c r="M90">
-        <v>187.5536256</v>
+        <v>189.6849168</v>
       </c>
       <c r="N90">
-        <v>-80.45362560000001</v>
+        <v>-82.58491680000003</v>
       </c>
       <c r="O90">
-        <v>-16.09072512</v>
+        <v>-16.51698336000001</v>
       </c>
       <c r="P90">
-        <v>-64.36290048000001</v>
+        <v>-66.06793344000002</v>
       </c>
       <c r="Q90">
-        <v>49.53709952</v>
+        <v>47.83206655999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4104790541033198</v>
+        <v>0.4436316953854398</v>
       </c>
       <c r="T90">
-        <v>3.993385115596283</v>
+        <v>4.356420126105036</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1142073363363443</v>
+        <v>0.1129241078381831</v>
       </c>
       <c r="W90">
-        <v>0.1778671668636621</v>
+        <v>0.1781248391460928</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5710366816817216</v>
+        <v>0.5646205391909157</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.207330593332421</v>
+        <v>0.208880593332421</v>
       </c>
       <c r="C91">
-        <v>-466.9785089990694</v>
+        <v>-480.966913716189</v>
       </c>
       <c r="D91">
-        <v>403.8674910009307</v>
+        <v>400.4930862838111</v>
       </c>
       <c r="E91">
-        <v>639.1460000000001</v>
+        <v>649.7600000000001</v>
       </c>
       <c r="F91">
-        <v>944.6460000000001</v>
+        <v>955.2600000000001</v>
       </c>
       <c r="G91">
         <v>73.8</v>
@@ -8749,37 +8749,37 @@
         <v>107.1</v>
       </c>
       <c r="M91">
-        <v>189.6849168</v>
+        <v>191.816208</v>
       </c>
       <c r="N91">
-        <v>-82.58491680000003</v>
+        <v>-84.71620800000002</v>
       </c>
       <c r="O91">
-        <v>-16.51698336000001</v>
+        <v>-16.9432416</v>
       </c>
       <c r="P91">
-        <v>-66.06793344000002</v>
+        <v>-67.77296640000002</v>
       </c>
       <c r="Q91">
-        <v>47.83206655999999</v>
+        <v>46.12703359999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4436316953854398</v>
+        <v>0.4834148649239838</v>
       </c>
       <c r="T91">
-        <v>4.356420126105036</v>
+        <v>4.792062138715539</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1129241078381831</v>
+        <v>0.11166939552887</v>
       </c>
       <c r="W91">
-        <v>0.1781248391460928</v>
+        <v>0.1783767853778029</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5646205391909157</v>
+        <v>0.5583469776443499</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.208880593332421</v>
+        <v>0.210430593332421</v>
       </c>
       <c r="C92">
-        <v>-480.966913716189</v>
+        <v>-494.899397825362</v>
       </c>
       <c r="D92">
-        <v>400.4930862838111</v>
+        <v>397.1746021746381</v>
       </c>
       <c r="E92">
-        <v>649.7600000000001</v>
+        <v>660.3740000000001</v>
       </c>
       <c r="F92">
-        <v>955.2600000000001</v>
+        <v>965.8740000000001</v>
       </c>
       <c r="G92">
         <v>73.8</v>
@@ -8831,37 +8831,37 @@
         <v>107.1</v>
       </c>
       <c r="M92">
-        <v>191.816208</v>
+        <v>193.9474992</v>
       </c>
       <c r="N92">
-        <v>-84.71620800000002</v>
+        <v>-86.84749920000004</v>
       </c>
       <c r="O92">
-        <v>-16.9432416</v>
+        <v>-17.36949984000001</v>
       </c>
       <c r="P92">
-        <v>-67.77296640000002</v>
+        <v>-69.47799936000004</v>
       </c>
       <c r="Q92">
-        <v>46.12703359999999</v>
+        <v>44.42200063999996</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4834148649239838</v>
+        <v>0.5320387388044265</v>
       </c>
       <c r="T92">
-        <v>4.792062138715539</v>
+        <v>5.324513487461711</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.11166939552887</v>
+        <v>0.110442259314267</v>
       </c>
       <c r="W92">
-        <v>0.1783767853778029</v>
+        <v>0.1786231943296952</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5583469776443499</v>
+        <v>0.5522112965713351</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.210430593332421</v>
+        <v>0.211980593332421</v>
       </c>
       <c r="C93">
-        <v>-494.899397825362</v>
+        <v>-508.7773399768982</v>
       </c>
       <c r="D93">
-        <v>397.1746021746381</v>
+        <v>393.910660023102</v>
       </c>
       <c r="E93">
-        <v>660.3740000000001</v>
+        <v>670.9880000000002</v>
       </c>
       <c r="F93">
-        <v>965.8740000000001</v>
+        <v>976.4880000000002</v>
       </c>
       <c r="G93">
         <v>73.8</v>
@@ -8913,37 +8913,37 @@
         <v>107.1</v>
       </c>
       <c r="M93">
-        <v>193.9474992</v>
+        <v>196.0787904</v>
       </c>
       <c r="N93">
-        <v>-86.84749920000004</v>
+        <v>-88.97879040000004</v>
       </c>
       <c r="O93">
-        <v>-17.36949984000001</v>
+        <v>-17.79575808000001</v>
       </c>
       <c r="P93">
-        <v>-69.47799936000004</v>
+        <v>-71.18303232000002</v>
       </c>
       <c r="Q93">
-        <v>44.42200063999996</v>
+        <v>42.71696767999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5320387388044265</v>
+        <v>0.5928185811549799</v>
       </c>
       <c r="T93">
-        <v>5.324513487461711</v>
+        <v>5.990077673394427</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.110442259314267</v>
+        <v>0.1092417999738946</v>
       </c>
       <c r="W93">
-        <v>0.1786231943296952</v>
+        <v>0.178864246565242</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5522112965713351</v>
+        <v>0.5462089998694728</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.211980593332421</v>
+        <v>0.213530593332421</v>
       </c>
       <c r="C94">
-        <v>-508.7773399768982</v>
+        <v>-522.6020738720388</v>
       </c>
       <c r="D94">
-        <v>393.910660023102</v>
+        <v>390.6999261279614</v>
       </c>
       <c r="E94">
-        <v>670.9880000000002</v>
+        <v>681.6020000000001</v>
       </c>
       <c r="F94">
-        <v>976.4880000000002</v>
+        <v>987.1020000000001</v>
       </c>
       <c r="G94">
         <v>73.8</v>
@@ -8995,37 +8995,37 @@
         <v>107.1</v>
       </c>
       <c r="M94">
-        <v>196.0787904</v>
+        <v>198.2100816</v>
       </c>
       <c r="N94">
-        <v>-88.97879040000004</v>
+        <v>-91.11008160000003</v>
       </c>
       <c r="O94">
-        <v>-17.79575808000001</v>
+        <v>-18.22201632000001</v>
       </c>
       <c r="P94">
-        <v>-71.18303232000002</v>
+        <v>-72.88806528000002</v>
       </c>
       <c r="Q94">
-        <v>42.71696767999998</v>
+        <v>41.01193471999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5928185811549799</v>
+        <v>0.6709640927485485</v>
       </c>
       <c r="T94">
-        <v>5.990077673394427</v>
+        <v>6.845803055307917</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1092417999738946</v>
+        <v>0.1080671569634226</v>
       </c>
       <c r="W94">
-        <v>0.178864246565242</v>
+        <v>0.1791001148817447</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5462089998694728</v>
+        <v>0.5403357848171129</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.213530593332421</v>
+        <v>0.215080593332421</v>
       </c>
       <c r="C95">
-        <v>-522.6020738720388</v>
+        <v>-536.3748900800274</v>
       </c>
       <c r="D95">
-        <v>390.6999261279614</v>
+        <v>387.5411099199727</v>
       </c>
       <c r="E95">
-        <v>681.6020000000001</v>
+        <v>692.2160000000001</v>
       </c>
       <c r="F95">
-        <v>987.1020000000001</v>
+        <v>997.7160000000001</v>
       </c>
       <c r="G95">
         <v>73.8</v>
@@ -9077,37 +9077,37 @@
         <v>107.1</v>
       </c>
       <c r="M95">
-        <v>198.2100816</v>
+        <v>200.3413728</v>
       </c>
       <c r="N95">
-        <v>-91.11008160000003</v>
+        <v>-93.24137280000005</v>
       </c>
       <c r="O95">
-        <v>-18.22201632000001</v>
+        <v>-18.64827456000001</v>
       </c>
       <c r="P95">
-        <v>-72.88806528000002</v>
+        <v>-74.59309824000005</v>
       </c>
       <c r="Q95">
-        <v>41.01193471999999</v>
+        <v>39.30690175999996</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6709640927485485</v>
+        <v>0.7751581082066402</v>
       </c>
       <c r="T95">
-        <v>6.845803055307917</v>
+        <v>7.986770231192573</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1080671569634226</v>
+        <v>0.1069175063574287</v>
       </c>
       <c r="W95">
-        <v>0.1791001148817447</v>
+        <v>0.1793309647234283</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5403357848171129</v>
+        <v>0.5345875317871436</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.215080593332421</v>
+        <v>0.216630593332421</v>
       </c>
       <c r="C96">
-        <v>-536.3748900800274</v>
+        <v>-550.0970377677409</v>
       </c>
       <c r="D96">
-        <v>387.5411099199727</v>
+        <v>384.4329622322593</v>
       </c>
       <c r="E96">
-        <v>692.2160000000001</v>
+        <v>702.8300000000002</v>
       </c>
       <c r="F96">
-        <v>997.7160000000001</v>
+        <v>1008.33</v>
       </c>
       <c r="G96">
         <v>73.8</v>
@@ -9159,37 +9159,37 @@
         <v>107.1</v>
       </c>
       <c r="M96">
-        <v>200.3413728</v>
+        <v>202.472664</v>
       </c>
       <c r="N96">
-        <v>-93.24137280000005</v>
+        <v>-95.37266400000004</v>
       </c>
       <c r="O96">
-        <v>-18.64827456000001</v>
+        <v>-19.07453280000001</v>
       </c>
       <c r="P96">
-        <v>-74.59309824000005</v>
+        <v>-76.29813120000003</v>
       </c>
       <c r="Q96">
-        <v>39.30690175999996</v>
+        <v>37.60186879999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7751581082066402</v>
+        <v>0.9210297298479688</v>
       </c>
       <c r="T96">
-        <v>7.986770231192573</v>
+        <v>9.584124277431092</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1069175063574287</v>
+        <v>0.1057920589220874</v>
       </c>
       <c r="W96">
-        <v>0.1793309647234283</v>
+        <v>0.1795569545684449</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5345875317871436</v>
+        <v>0.5289602946104368</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.216630593332421</v>
+        <v>0.218180593332421</v>
       </c>
       <c r="C97">
-        <v>-550.0970377677409</v>
+        <v>-563.7697263467498</v>
       </c>
       <c r="D97">
-        <v>384.4329622322593</v>
+        <v>381.3742736532503</v>
       </c>
       <c r="E97">
-        <v>702.8300000000002</v>
+        <v>713.4440000000002</v>
       </c>
       <c r="F97">
-        <v>1008.33</v>
+        <v>1018.944</v>
       </c>
       <c r="G97">
         <v>73.8</v>
@@ -9241,37 +9241,37 @@
         <v>107.1</v>
       </c>
       <c r="M97">
-        <v>202.472664</v>
+        <v>204.6039552</v>
       </c>
       <c r="N97">
-        <v>-95.37266400000004</v>
+        <v>-97.50395520000004</v>
       </c>
       <c r="O97">
-        <v>-19.07453280000001</v>
+        <v>-19.50079104000001</v>
       </c>
       <c r="P97">
-        <v>-76.29813120000003</v>
+        <v>-78.00316416000003</v>
       </c>
       <c r="Q97">
-        <v>37.60186879999998</v>
+        <v>35.89683583999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9210297298479688</v>
+        <v>1.139837162309961</v>
       </c>
       <c r="T97">
-        <v>9.584124277431092</v>
+        <v>11.98015534678887</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1057920589220874</v>
+        <v>0.1046900583083156</v>
       </c>
       <c r="W97">
-        <v>0.1795569545684449</v>
+        <v>0.1797782362916902</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5289602946104368</v>
+        <v>0.5234502915415781</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.218180593332421</v>
+        <v>0.219730593332421</v>
       </c>
       <c r="C98">
-        <v>-563.7697263467496</v>
+        <v>-577.3941270423743</v>
       </c>
       <c r="D98">
-        <v>381.3742736532504</v>
+        <v>378.3638729576257</v>
       </c>
       <c r="E98">
-        <v>713.4440000000001</v>
+        <v>724.058</v>
       </c>
       <c r="F98">
-        <v>1018.944</v>
+        <v>1029.558</v>
       </c>
       <c r="G98">
         <v>73.8</v>
@@ -9323,37 +9323,37 @@
         <v>107.1</v>
       </c>
       <c r="M98">
-        <v>204.6039552</v>
+        <v>206.7352464</v>
       </c>
       <c r="N98">
-        <v>-97.50395520000004</v>
+        <v>-99.6352464</v>
       </c>
       <c r="O98">
-        <v>-19.50079104000001</v>
+        <v>-19.92704928</v>
       </c>
       <c r="P98">
-        <v>-78.00316416000003</v>
+        <v>-79.70819711999999</v>
       </c>
       <c r="Q98">
-        <v>35.89683583999998</v>
+        <v>34.19180288000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.139837162309958</v>
+        <v>1.504516216413278</v>
       </c>
       <c r="T98">
-        <v>11.98015534678884</v>
+        <v>15.97354046238512</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1046900583083156</v>
+        <v>0.1036107793566835</v>
       </c>
       <c r="W98">
-        <v>0.1797782362916902</v>
+        <v>0.179994955505178</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5234502915415781</v>
+        <v>0.5180538967834176</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.219730593332421</v>
+        <v>0.221280593332421</v>
       </c>
       <c r="C99">
-        <v>-577.3941270423743</v>
+        <v>-590.9713743890079</v>
       </c>
       <c r="D99">
-        <v>378.3638729576257</v>
+        <v>375.4006256109921</v>
       </c>
       <c r="E99">
-        <v>724.058</v>
+        <v>734.672</v>
       </c>
       <c r="F99">
-        <v>1029.558</v>
+        <v>1040.172</v>
       </c>
       <c r="G99">
         <v>73.8</v>
@@ -9405,37 +9405,37 @@
         <v>107.1</v>
       </c>
       <c r="M99">
-        <v>206.7352464</v>
+        <v>208.8665376</v>
       </c>
       <c r="N99">
-        <v>-99.6352464</v>
+        <v>-101.7665376</v>
       </c>
       <c r="O99">
-        <v>-19.92704928</v>
+        <v>-20.35330752</v>
       </c>
       <c r="P99">
-        <v>-79.70819711999999</v>
+        <v>-81.41323008000002</v>
       </c>
       <c r="Q99">
-        <v>34.19180288000001</v>
+        <v>32.48676991999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.504516216413278</v>
+        <v>2.233874324619916</v>
       </c>
       <c r="T99">
-        <v>15.97354046238512</v>
+        <v>23.96031069357767</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1036107793566835</v>
+        <v>0.1025535265061051</v>
       </c>
       <c r="W99">
-        <v>0.179994955505178</v>
+        <v>0.1802072518775741</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5180538967834176</v>
+        <v>0.5127676325305255</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.221280593332421</v>
+        <v>0.222830593332421</v>
       </c>
       <c r="C100">
-        <v>-590.9713743890079</v>
+        <v>-604.5025676557202</v>
       </c>
       <c r="D100">
-        <v>375.4006256109921</v>
+        <v>372.4834323442799</v>
       </c>
       <c r="E100">
-        <v>734.672</v>
+        <v>745.2860000000001</v>
       </c>
       <c r="F100">
-        <v>1040.172</v>
+        <v>1050.786</v>
       </c>
       <c r="G100">
         <v>73.8</v>
@@ -9487,37 +9487,37 @@
         <v>107.1</v>
       </c>
       <c r="M100">
-        <v>208.8665376</v>
+        <v>210.9978288</v>
       </c>
       <c r="N100">
-        <v>-101.7665376</v>
+        <v>-103.8978288</v>
       </c>
       <c r="O100">
-        <v>-20.35330752</v>
+        <v>-20.77956576</v>
       </c>
       <c r="P100">
-        <v>-81.41323008000002</v>
+        <v>-83.11826304000002</v>
       </c>
       <c r="Q100">
-        <v>32.48676991999999</v>
+        <v>30.78173695999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.233874324619916</v>
+        <v>4.421948649239833</v>
       </c>
       <c r="T100">
-        <v>23.96031069357767</v>
+        <v>47.92062138715534</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1025535265061051</v>
+        <v>0.1015176322989727</v>
       </c>
       <c r="W100">
-        <v>0.1802072518775741</v>
+        <v>0.1804152594343663</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5127676325305255</v>
+        <v>0.5075881614948636</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.222830593332421</v>
-      </c>
-      <c r="C101">
-        <v>-604.5025676557202</v>
-      </c>
-      <c r="D101">
-        <v>372.4834323442799</v>
-      </c>
-      <c r="E101">
-        <v>745.2860000000001</v>
-      </c>
-      <c r="F101">
-        <v>1050.786</v>
-      </c>
-      <c r="G101">
-        <v>73.8</v>
-      </c>
-      <c r="H101">
-        <v>755.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>221</v>
-      </c>
-      <c r="K101">
-        <v>113.9</v>
-      </c>
-      <c r="L101">
-        <v>107.1</v>
-      </c>
-      <c r="M101">
-        <v>210.9978288</v>
-      </c>
-      <c r="N101">
-        <v>-103.8978288</v>
-      </c>
-      <c r="O101">
-        <v>-20.77956576</v>
-      </c>
-      <c r="P101">
-        <v>-83.11826304000002</v>
-      </c>
-      <c r="Q101">
-        <v>30.78173695999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.421948649239833</v>
-      </c>
-      <c r="T101">
-        <v>47.92062138715534</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1015176322989727</v>
-      </c>
-      <c r="W101">
-        <v>0.1804152594343663</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5075881614948636</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
